--- a/src/attributions/attributions_saliency_traj_81.xlsx
+++ b/src/attributions/attributions_saliency_traj_81.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG14"/>
+  <dimension ref="A1:GG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.07020905613899231</v>
+        <v>8.937903658079449e-06</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6487566232681274</v>
+        <v>0.0001656328531680629</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03047627210617065</v>
+        <v>1.587007318448741e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0850573405623436</v>
+        <v>6.202718941494823e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08047193288803101</v>
+        <v>3.059092705370858e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08449524641036987</v>
+        <v>0.0001366039796266705</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2080699801445007</v>
+        <v>0.0001051980143529363</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2492536604404449</v>
+        <v>8.843255272950046e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.42540243268013</v>
+        <v>0.0001291004737140611</v>
       </c>
       <c r="J2" t="n">
-        <v>0.07465451210737228</v>
+        <v>2.359211612201761e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5601475834846497</v>
+        <v>0.0002092359500238672</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01850273087620735</v>
+        <v>2.964947998407297e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3031962811946869</v>
+        <v>0.0001275981194339693</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05210050195455551</v>
+        <v>9.017452248372138e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06150791794061661</v>
+        <v>0.0001971522287931293</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2379152923822403</v>
+        <v>1.05411272670608e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.200376033782959</v>
+        <v>0.0001188736059702933</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4118303656578064</v>
+        <v>0.0001566394930705428</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004137981217354536</v>
+        <v>1.051094295689836e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>0.09910774230957031</v>
+        <v>3.966368240071461e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02565426751971245</v>
+        <v>8.179018550436012e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>0.04193956032395363</v>
+        <v>3.693871985888109e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>0.08043920993804932</v>
+        <v>1.165151206805604e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>0.07157657295465469</v>
+        <v>7.057894981699064e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01364984456449747</v>
+        <v>2.753627995843999e-05</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.04631437361240387</v>
+        <v>1.571490429341793e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03205519914627075</v>
+        <v>5.191290256334469e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.05711104348301888</v>
+        <v>6.009039680066053e-06</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.05225816741585732</v>
+        <v>2.154484172933735e-05</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1674928665161133</v>
+        <v>1.330787290498847e-05</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.006820600479841232</v>
+        <v>0.0001402921334374696</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1457177102565765</v>
+        <v>1.181618790724315e-05</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.120751328766346</v>
+        <v>4.382866245578043e-05</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0106296194717288</v>
+        <v>1.829960820032284e-05</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.1299783438444138</v>
+        <v>2.621853491291404e-05</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1320647150278091</v>
+        <v>3.085015487158671e-05</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.05853741243481636</v>
+        <v>8.003845323401038e-06</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.02940265834331512</v>
+        <v>3.040586125280242e-05</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.00969654880464077</v>
+        <v>4.470263775147032e-06</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.06120211631059647</v>
+        <v>5.299016629578546e-05</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.007105840370059013</v>
+        <v>5.820598744321615e-06</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.02998600155115128</v>
+        <v>2.537796535762027e-05</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.009127735160291195</v>
+        <v>9.057592251338065e-06</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.01264873519539833</v>
+        <v>1.321702711720718e-06</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.005668124184012413</v>
+        <v>1.489998885517707e-05</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.05467565357685089</v>
+        <v>1.055510074365884e-05</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4572664797306061</v>
+        <v>0.0001947534619830549</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.07591357827186584</v>
+        <v>8.124570740619674e-06</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1210866197943687</v>
+        <v>8.520350093021989e-05</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1745174825191498</v>
+        <v>8.993899973575026e-05</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0130835548043251</v>
+        <v>6.171504355734214e-05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1726005673408508</v>
+        <v>2.974964445456862e-05</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.08916446566581726</v>
+        <v>4.574142803903669e-05</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.1206597462296486</v>
+        <v>8.702765626367182e-05</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.08421188592910767</v>
+        <v>1.210396385431523e-05</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.09106536209583282</v>
+        <v>3.755276338779368e-05</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.07450021803379059</v>
+        <v>3.903024662577081e-06</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.04937668889760971</v>
+        <v>1.652434366405942e-05</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.03618676587939262</v>
+        <v>1.87044406629866e-05</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.1072970777750015</v>
+        <v>7.57999368943274e-05</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.02472755499184132</v>
+        <v>3.532495975377969e-05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.01224677264690399</v>
+        <v>5.195400808588602e-05</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.2646457552909851</v>
+        <v>3.115684376098216e-05</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.08263009041547775</v>
+        <v>1.977078136405908e-05</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.03381972759962082</v>
+        <v>1.339303707936779e-07</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.02357932925224304</v>
+        <v>1.899076596600935e-05</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.00453877029940486</v>
+        <v>1.503704334027134e-05</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.263441413640976</v>
+        <v>3.04218046949245e-05</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.1028799712657928</v>
+        <v>5.753017467213795e-05</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.0683199018239975</v>
+        <v>7.527077104896307e-05</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.04362655803561211</v>
+        <v>6.111077527748421e-05</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.05050981789827347</v>
+        <v>3.877679409924895e-05</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.03686298802495003</v>
+        <v>9.844825399341062e-07</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2666178345680237</v>
+        <v>0.000109535627416335</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.06267877668142319</v>
+        <v>1.889765917439945e-05</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.04142360761761665</v>
+        <v>5.206153582548723e-05</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.06415822356939316</v>
+        <v>6.608868716284633e-05</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.04088474437594414</v>
+        <v>2.874797246477101e-05</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.09535863995552063</v>
+        <v>4.410168185131624e-05</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.08452614396810532</v>
+        <v>9.954429515346419e-06</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.05895891785621643</v>
+        <v>6.840891728643328e-05</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.003969223238527775</v>
+        <v>8.751980203669518e-06</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1023536995053291</v>
+        <v>6.165279046399519e-05</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.0168111938983202</v>
+        <v>1.401548706780886e-05</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.0350419394671917</v>
+        <v>2.853547994163819e-05</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.03127208352088928</v>
+        <v>1.020596755552106e-05</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.006376609206199646</v>
+        <v>2.184823279094417e-05</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.03608233481645584</v>
+        <v>2.573669917182997e-05</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.01749134436249733</v>
+        <v>3.456408876445494e-06</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.09107811748981476</v>
+        <v>3.939973248634487e-05</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.02585260570049286</v>
+        <v>3.153916622977704e-05</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.07903662323951721</v>
+        <v>7.360293238889426e-05</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.007390481885522604</v>
+        <v>2.647158544277772e-05</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.1228092908859253</v>
+        <v>0.0001390981924487278</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.1624604165554047</v>
+        <v>0.0001072189552360214</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.08796752244234085</v>
+        <v>4.70960840175394e-05</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.02437302283942699</v>
+        <v>2.052470154012553e-05</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.09544286131858826</v>
+        <v>2.201344977947883e-05</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.1195762231945992</v>
+        <v>2.734876034082845e-05</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0002684115897864103</v>
+        <v>2.14991596294567e-05</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.1216698214411736</v>
+        <v>5.664246782544069e-05</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.04375426098704338</v>
+        <v>1.507181332272012e-05</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.02964390255510807</v>
+        <v>4.030339187011123e-05</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.03707441315054893</v>
+        <v>1.228968812938547e-05</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.002252088859677315</v>
+        <v>3.001783261424862e-05</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.03992631286382675</v>
+        <v>1.757085192366503e-05</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.01547718327492476</v>
+        <v>1.973563666979317e-05</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.06166895106434822</v>
+        <v>5.044832869316451e-05</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.07861444354057312</v>
+        <v>1.805049396352842e-05</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.1274753212928772</v>
+        <v>3.518716403050348e-05</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.05623171851038933</v>
+        <v>1.138243987952592e-06</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.1392171382904053</v>
+        <v>2.979643613798544e-05</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.00438418798148632</v>
+        <v>6.335914804367349e-05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.005496605765074492</v>
+        <v>3.795206430368125e-05</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.04386424273252487</v>
+        <v>5.625273479381576e-05</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.03053396195173264</v>
+        <v>3.199210914317518e-05</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.03343762084841728</v>
+        <v>6.432813097489998e-05</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.08050775527954102</v>
+        <v>6.973356448725099e-06</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.09232806414365768</v>
+        <v>1.465623427066021e-05</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.005429161712527275</v>
+        <v>5.691614205716178e-06</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.08708608150482178</v>
+        <v>1.599775714566931e-05</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0631997287273407</v>
+        <v>5.259285171632655e-05</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.01440035924315453</v>
+        <v>3.075512358918786e-05</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.09019777178764343</v>
+        <v>2.288068571942858e-05</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.01213292591273785</v>
+        <v>2.708709325816017e-05</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.1464402079582214</v>
+        <v>4.47633137810044e-05</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.05017918720841408</v>
+        <v>9.954887900676113e-06</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.1161086708307266</v>
+        <v>1.313325083174277e-05</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.01116050686687231</v>
+        <v>1.410221557307523e-06</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.04230877757072449</v>
+        <v>1.76243429450551e-05</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.07139588892459869</v>
+        <v>9.07929461391177e-06</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.03423966839909554</v>
+        <v>5.112684448249638e-05</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.0009175166487693787</v>
+        <v>7.307984560611658e-06</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.09126149117946625</v>
+        <v>1.492773844802286e-05</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.01288665644824505</v>
+        <v>3.226078842999414e-05</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.02685352228581905</v>
+        <v>1.158822124125436e-05</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.001729525625705719</v>
+        <v>4.914175224257633e-05</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.04767151921987534</v>
+        <v>1.335644446953665e-05</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.02284050174057484</v>
+        <v>2.614700861158781e-05</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.1302188634872437</v>
+        <v>7.634309440618381e-06</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.00805626530200243</v>
+        <v>1.666828393354081e-05</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.04678854718804359</v>
+        <v>9.973325177270453e-06</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.08155959099531174</v>
+        <v>6.212710286490619e-05</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.1017944067716599</v>
+        <v>7.807492693245877e-06</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.0351814366877079</v>
+        <v>1.727146081975661e-05</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.00127063225954771</v>
+        <v>2.370395668549463e-05</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.05908995121717453</v>
+        <v>9.923172910930589e-06</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.1300375908613205</v>
+        <v>3.477099380688742e-05</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.06115130335092545</v>
+        <v>3.857384217553772e-05</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.05651354417204857</v>
+        <v>7.283871582330903e-06</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.005614995956420898</v>
+        <v>2.661898543010466e-05</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.03017267026007175</v>
+        <v>4.577183426590636e-05</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.05004310980439186</v>
+        <v>8.766163955442607e-05</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.01312299072742462</v>
+        <v>1.212535516970092e-05</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.1139889135956764</v>
+        <v>6.710386514896527e-05</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.02107577957212925</v>
+        <v>1.286621409235522e-05</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.00190312578342855</v>
+        <v>4.104337131138891e-05</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.0244462639093399</v>
+        <v>5.926919584453572e-06</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.01548696868121624</v>
+        <v>1.533421163912863e-05</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.05194130539894104</v>
+        <v>1.983428410312627e-05</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.01281412318348885</v>
+        <v>2.868069714168087e-06</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.07370483875274658</v>
+        <v>3.50524605892133e-05</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.003232622519135475</v>
+        <v>9.131976185017265e-06</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.07450377196073532</v>
+        <v>5.822935054311529e-05</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.02668399922549725</v>
+        <v>1.382843765895814e-05</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.0236673504114151</v>
+        <v>4.750756488647312e-05</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.1820880919694901</v>
+        <v>4.649976290238556e-06</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.01832257956266403</v>
+        <v>8.920792424760293e-06</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.01732836849987507</v>
+        <v>1.44451360029052e-05</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.02262798696756363</v>
+        <v>7.018571341177449e-05</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.07654521614313126</v>
+        <v>6.519079033751041e-05</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.03826713934540749</v>
+        <v>2.062806743197143e-05</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.1825832724571228</v>
+        <v>5.074691944173537e-05</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.004152100533246994</v>
+        <v>3.181197826052085e-05</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.08067534118890762</v>
+        <v>3.06866058963351e-05</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.09465967118740082</v>
+        <v>1.449220872018486e-05</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.03722536191344261</v>
+        <v>4.605761205311865e-05</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.07109362632036209</v>
+        <v>5.124712697579525e-05</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.06496850401163101</v>
+        <v>5.752236756961793e-05</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.07481802999973297</v>
+        <v>2.956435855594464e-05</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.05687084794044495</v>
+        <v>2.997737283294555e-05</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.08184947073459625</v>
+        <v>1.199422695208341e-05</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.01407152973115444</v>
+        <v>5.544174200622365e-05</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.06984031200408936</v>
+        <v>1.118706131819636e-05</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.1015651673078537</v>
+        <v>2.797009074129164e-05</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.07590136677026749</v>
+        <v>6.035730621078983e-05</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.05251242592930794</v>
+        <v>7.734064274700359e-05</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.009639736264944077</v>
+        <v>4.215434455545619e-05</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.01624035462737083</v>
+        <v>2.049191971309483e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2706,571 +2706,571 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.03264297544956207</v>
+        <v>2.631743882375304e-06</v>
       </c>
       <c r="B5" t="n">
-        <v>0.619964599609375</v>
+        <v>1.0824657692865e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07405433058738708</v>
+        <v>6.355298410198884e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2031481266021729</v>
+        <v>5.369130121835042e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08285133540630341</v>
+        <v>1.361137947242241e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09346573054790497</v>
+        <v>6.699381174257724e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2839886546134949</v>
+        <v>4.140336841373937e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0376201719045639</v>
+        <v>3.494926886560279e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01950432173907757</v>
+        <v>9.314164344687015e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.112714558839798</v>
+        <v>2.477102498232853e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5556818842887878</v>
+        <v>1.509291087131714e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03684507682919502</v>
+        <v>6.522416697407607e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2629537284374237</v>
+        <v>7.035221642581746e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06763920187950134</v>
+        <v>2.035850229731295e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1551095247268677</v>
+        <v>2.867623152269516e-06</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2534741759300232</v>
+        <v>8.613224053988233e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.09901884943246841</v>
+        <v>4.736237315228209e-06</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001966154202818871</v>
+        <v>4.59570401289966e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05584324151277542</v>
+        <v>8.529448791705363e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07318592071533203</v>
+        <v>2.743874119914835e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0480097234249115</v>
+        <v>1.69385600656824e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01536856964230537</v>
+        <v>1.239229732163949e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0845988467335701</v>
+        <v>5.122267339174869e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02030616067349911</v>
+        <v>3.984540398960235e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003534365445375443</v>
+        <v>2.880110741898534e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.06259704381227493</v>
+        <v>2.378279049253251e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.09190671890974045</v>
+        <v>6.637333626713371e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01272455602884293</v>
+        <v>4.901308784610592e-06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.03861488401889801</v>
+        <v>3.226601847927668e-06</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.03158246725797653</v>
+        <v>2.823804607032798e-06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.04685376957058907</v>
+        <v>2.720227030295064e-06</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.04530632868409157</v>
+        <v>2.100659003190231e-06</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.07313006371259689</v>
+        <v>1.911791969178012e-06</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.01730412244796753</v>
+        <v>1.981938339667977e-06</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.005397798493504524</v>
+        <v>4.835014237869473e-07</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.04169329628348351</v>
+        <v>1.3513829344447e-06</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.05148806795477867</v>
+        <v>3.295973556305398e-07</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.07558112591505051</v>
+        <v>8.110584985843161e-07</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.01295486651360989</v>
+        <v>5.727318921344704e-07</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.02769482880830765</v>
+        <v>1.330621785200492e-06</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.02148770727217197</v>
+        <v>6.34584296221874e-07</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.03264578431844711</v>
+        <v>1.524669187347172e-06</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.03336608409881592</v>
+        <v>1.158844042947749e-08</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.01236812770366669</v>
+        <v>2.747391590673942e-06</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.04026047512888908</v>
+        <v>3.064347765757702e-06</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.08574257791042328</v>
+        <v>2.160642509352328e-08</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.4348281025886536</v>
+        <v>1.078509558283258e-05</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.06031670421361923</v>
+        <v>2.898138291129726e-06</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.06099729612469673</v>
+        <v>1.852930381573969e-06</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.058426633477211</v>
+        <v>1.137377012128127e-06</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.01776907593011856</v>
+        <v>1.947670853041927e-06</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1853493750095367</v>
+        <v>9.441887982575281e-07</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.02765889279544353</v>
+        <v>5.205428351473529e-06</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.07481499761343002</v>
+        <v>9.136217613558983e-07</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.01934673264622688</v>
+        <v>3.150323209410999e-06</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1639454960823059</v>
+        <v>3.57514636561973e-06</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.1572205424308777</v>
+        <v>3.922697942471132e-06</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.07670669257640839</v>
+        <v>1.177402737084776e-06</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.09195440262556076</v>
+        <v>1.260663111679605e-07</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.07629325985908508</v>
+        <v>5.500247425516136e-06</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.00686059333384037</v>
+        <v>1.075409954864881e-06</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.08863827586174011</v>
+        <v>4.386130058264825e-06</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.02229546941816807</v>
+        <v>1.239944504050072e-05</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.02137655019760132</v>
+        <v>1.528046141174855e-06</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.04392371699213982</v>
+        <v>4.999656653126294e-07</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0604507252573967</v>
+        <v>1.562899797136197e-06</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.09775357693433762</v>
+        <v>1.35061753780974e-07</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1431774795055389</v>
+        <v>3.067141278734198e-06</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.006363257765769958</v>
+        <v>3.376174390723463e-06</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.06516312807798386</v>
+        <v>1.365292661148487e-07</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.07195721566677094</v>
+        <v>2.27491887017095e-06</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.000350679736584425</v>
+        <v>1.129610041061824e-06</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.03932300209999084</v>
+        <v>1.412724486726802e-06</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1953675150871277</v>
+        <v>3.311176442366559e-06</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.06299888342618942</v>
+        <v>2.059932512565865e-06</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.02267098426818848</v>
+        <v>3.551325107764569e-06</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0236281119287014</v>
+        <v>3.343399441746442e-07</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.02253672853112221</v>
+        <v>4.9373247748008e-06</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.05480369180440903</v>
+        <v>2.060107362922281e-06</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.05170721933245659</v>
+        <v>1.350571551483881e-06</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.06650853902101517</v>
+        <v>1.902287181110296e-06</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.006139322184026241</v>
+        <v>8.935373898566468e-07</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1123599633574486</v>
+        <v>2.576140332166688e-06</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.05161983892321587</v>
+        <v>6.674906671833014e-07</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.03459374606609344</v>
+        <v>1.795854132069508e-09</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.004298896063119173</v>
+        <v>1.227780899171194e-06</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0005652706604450941</v>
+        <v>2.153358764189761e-06</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.06866946816444397</v>
+        <v>1.012957682178239e-06</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.003072809427976608</v>
+        <v>2.225662001364981e-07</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.03839148208498955</v>
+        <v>9.414180226485769e-07</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.136482298374176</v>
+        <v>3.673283572425134e-06</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.110665038228035</v>
+        <v>2.402499831077876e-06</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.01047609001398087</v>
+        <v>1.63045456247346e-07</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.1006714701652527</v>
+        <v>1.253628965969256e-06</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.1286185681819916</v>
+        <v>1.71753606537095e-06</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.01024883426725864</v>
+        <v>4.688647095463239e-06</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.003800641745328903</v>
+        <v>2.158358483939082e-06</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.04158187657594681</v>
+        <v>6.263752311497228e-06</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.04404320940375328</v>
+        <v>3.997356543550268e-06</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.007415028288960457</v>
+        <v>7.284999696821615e-07</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.1014657616615295</v>
+        <v>3.192764552295557e-06</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.05240579321980476</v>
+        <v>4.070509760367713e-07</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0771278589963913</v>
+        <v>3.504679852994741e-07</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01464698649942875</v>
+        <v>8.360484002878366e-07</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.002549427095800638</v>
+        <v>1.960383315235958e-06</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.07816208153963089</v>
+        <v>9.463000196774374e-07</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0134368697181344</v>
+        <v>1.0512064818613e-06</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.02678997628390789</v>
+        <v>1.270202233172313e-06</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.002974427305161953</v>
+        <v>8.212022066800273e-07</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.06299444288015366</v>
+        <v>1.057738586496271e-06</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.02791481837630272</v>
+        <v>7.533911229984369e-06</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.1573687493801117</v>
+        <v>3.846880190394586e-06</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01489017251878977</v>
+        <v>4.018388153781416e-06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.007379030808806419</v>
+        <v>3.128975833988079e-07</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.04442580789327621</v>
+        <v>1.39488804506982e-06</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.00866230484098196</v>
+        <v>7.441713023581542e-07</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.05736644566059113</v>
+        <v>2.917205677022139e-07</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.03265504166483879</v>
+        <v>1.155471522906737e-07</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.06107594445347786</v>
+        <v>2.767526439129142e-07</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.04677552357316017</v>
+        <v>5.341746600606712e-07</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.01378409750759602</v>
+        <v>5.804949068988208e-06</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.07685360312461853</v>
+        <v>1.515643361926777e-06</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.004091537557542324</v>
+        <v>7.797661396580224e-07</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.02937308885157108</v>
+        <v>4.94043342769146e-06</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.04660547897219658</v>
+        <v>2.693506303330651e-06</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.03342596441507339</v>
+        <v>4.374979653221089e-06</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.007805837318301201</v>
+        <v>1.492827323090751e-06</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.06675083935260773</v>
+        <v>2.224329364253208e-06</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.01815747283399105</v>
+        <v>1.804721136977605e-07</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.05543722584843636</v>
+        <v>2.832143763953354e-06</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.02070312947034836</v>
+        <v>1.169240476883715e-06</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.03590717166662216</v>
+        <v>6.766340902686352e-06</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.002587012015283108</v>
+        <v>4.336631263868185e-06</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.01487414166331291</v>
+        <v>6.636386160607799e-07</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.01974146813154221</v>
+        <v>2.387177119089756e-06</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0193457156419754</v>
+        <v>6.102338829805376e-07</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.08539398014545441</v>
+        <v>5.475173566082958e-06</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.04180185496807098</v>
+        <v>1.234075170941651e-06</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.04008305072784424</v>
+        <v>6.42216946289409e-09</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.05060658603906631</v>
+        <v>3.852481711419387e-08</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.004476836882531643</v>
+        <v>1.271960599069644e-07</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.08415945619344711</v>
+        <v>1.419997829543718e-06</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.000751761719584465</v>
+        <v>9.256008297597873e-07</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.01913252659142017</v>
+        <v>4.837686446990119e-07</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0518944151699543</v>
+        <v>3.021176553374971e-07</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.03403031453490257</v>
+        <v>1.828209974519268e-06</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.08869937062263489</v>
+        <v>3.372387709532632e-06</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.06378927081823349</v>
+        <v>2.94212168228114e-06</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.03923249989748001</v>
+        <v>1.733191538733081e-06</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.04682912677526474</v>
+        <v>2.778491534627392e-06</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.08183937519788742</v>
+        <v>4.688207354774931e-06</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.06482462584972382</v>
+        <v>3.256344143665046e-06</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.001105654169805348</v>
+        <v>9.367255415781983e-07</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.01747251115739346</v>
+        <v>1.255274696632114e-06</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.09821975231170654</v>
+        <v>3.277308223914588e-06</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.04098863899707794</v>
+        <v>7.347922519329586e-07</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.05469114705920219</v>
+        <v>1.102313262890675e-08</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.02342677675187588</v>
+        <v>1.428522182322922e-06</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.004340716172009706</v>
+        <v>1.660273710513138e-06</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.08692050725221634</v>
+        <v>9.891854233501363e-07</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.006528727244585752</v>
+        <v>4.966681217410951e-07</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.04401789978146553</v>
+        <v>9.809150469664019e-07</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.03324390575289726</v>
+        <v>3.059632717850036e-06</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.008509639650583267</v>
+        <v>4.325018380768597e-06</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.06705372035503387</v>
+        <v>1.496366394349025e-06</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.01655101403594017</v>
+        <v>2.162627339430401e-07</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.03447916358709335</v>
+        <v>3.74804449165822e-06</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.03219974413514137</v>
+        <v>2.991716883116169e-06</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.004858138971030712</v>
+        <v>8.379136033909163e-07</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.04336211085319519</v>
+        <v>3.440354703343473e-06</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.05369169265031815</v>
+        <v>8.539929694961756e-06</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.07303883880376816</v>
+        <v>1.079510184354149e-06</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.09902017563581467</v>
+        <v>9.119563401327468e-06</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.1000688895583153</v>
+        <v>2.71947874352918e-06</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.09377869218587875</v>
+        <v>4.297697273614176e-07</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.04789320752024651</v>
+        <v>5.834408057125984e-06</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.004518410190939903</v>
+        <v>4.642491603590315e-06</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.003994235768914223</v>
+        <v>5.699318080587545e-06</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.02768679149448872</v>
+        <v>7.071267191349762e-06</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.06307300180196762</v>
+        <v>3.92433867091313e-06</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.08303193747997284</v>
+        <v>1.416586655977881e-06</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.07679401338100433</v>
+        <v>2.230077370768413e-06</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.007359413430094719</v>
+        <v>2.430929725960596e-06</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.03978590667247772</v>
+        <v>1.726149321257253e-06</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.04350365325808525</v>
+        <v>5.124036306369817e-06</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.03788527846336365</v>
+        <v>1.671662516855577e-06</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.1593970656394958</v>
+        <v>2.978141992571182e-06</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.1154135689139366</v>
+        <v>2.150140971934889e-07</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.01961808279156685</v>
+        <v>7.059277891130478e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3844,4554 +3844,5123 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.4296889305114746</v>
+        <v>0.01875900477170944</v>
       </c>
       <c r="B7" t="n">
-        <v>3.317833423614502</v>
+        <v>0.2619359195232391</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1261774599552155</v>
+        <v>0.1399182379245758</v>
       </c>
       <c r="D7" t="n">
-        <v>3.060757398605347</v>
+        <v>0.1359779834747314</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1742200404405594</v>
+        <v>0.1009256690740585</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7456098794937134</v>
+        <v>0.07797370105981827</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1055325120687485</v>
+        <v>0.04353701695799828</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3917349576950073</v>
+        <v>0.02046924084424973</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3040046095848083</v>
+        <v>0.01626485213637352</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1596112102270126</v>
+        <v>0.003718170570209622</v>
       </c>
       <c r="K7" t="n">
-        <v>2.711395740509033</v>
+        <v>0.2331796735525131</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2801417708396912</v>
+        <v>0.1051599681377411</v>
       </c>
       <c r="M7" t="n">
-        <v>2.74517297744751</v>
+        <v>0.2200383245944977</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1811942160129547</v>
+        <v>0.1420252323150635</v>
       </c>
       <c r="O7" t="n">
-        <v>1.125648617744446</v>
+        <v>0.1264919638633728</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02703186869621277</v>
+        <v>0.03494340926408768</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4063643515110016</v>
+        <v>0.02073091268539429</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6216322779655457</v>
+        <v>0.01276212930679321</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2966461479663849</v>
+        <v>0.01244466286152601</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2052700072526932</v>
+        <v>0.0244189128279686</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1209668815135956</v>
+        <v>0.02716494537889957</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4329040348529816</v>
+        <v>0.01497882045805454</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2342905402183533</v>
+        <v>0.007425589952617884</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1055474728345871</v>
+        <v>0.01253531966358423</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.310632199048996</v>
+        <v>0.004997742362320423</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6225250959396362</v>
+        <v>0.01023659948259592</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.547400951385498</v>
+        <v>0.02459830790758133</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3225113153457642</v>
+        <v>0.01941057853400707</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03995153307914734</v>
+        <v>0.02734545432031155</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.4085570871829987</v>
+        <v>0.03036772832274437</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.4806971549987793</v>
+        <v>0.01485705655068159</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.3372186124324799</v>
+        <v>0.02370559237897396</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.2043980062007904</v>
+        <v>0.0395815409719944</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1028364673256874</v>
+        <v>0.02257741987705231</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.2674514353275299</v>
+        <v>0.03104467131197453</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.4191342294216156</v>
+        <v>0.01907548680901527</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.03679867461323738</v>
+        <v>0.01684603095054626</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.3402172327041626</v>
+        <v>0.04287616536021233</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.02785783633589745</v>
+        <v>0.005994759500026703</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.2864362299442291</v>
+        <v>0.01749797537922859</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.1472232043743134</v>
+        <v>0.04048402234911919</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.175244465470314</v>
+        <v>0.007882943376898766</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.2276480793952942</v>
+        <v>0.005848174914717674</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.1072618216276169</v>
+        <v>0.005297394469380379</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.194654107093811</v>
+        <v>0.0006192345172166824</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.5647721886634827</v>
+        <v>0.006500632502138615</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.068906784057617</v>
+        <v>0.02430673688650131</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.1704080104827881</v>
+        <v>0.004460663534700871</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.053962826728821</v>
+        <v>0.05517099052667618</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1233387440443039</v>
+        <v>0.1348728537559509</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.2260532975196838</v>
+        <v>0.07641834765672684</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.2895184457302094</v>
+        <v>0.0001638606481719762</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.28488889336586</v>
+        <v>0.02210971340537071</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.4433553218841553</v>
+        <v>0.01303867623209953</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.08286375552415848</v>
+        <v>0.06100547686219215</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.5218585729598999</v>
+        <v>0.1637559682130814</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.6224251985549927</v>
+        <v>0.03552290797233582</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.055482387542725</v>
+        <v>0.01867723651230335</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.8099605441093445</v>
+        <v>0.009281719103455544</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.1028022840619087</v>
+        <v>0.003280825912952423</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.06258320808410645</v>
+        <v>0.0187881626188755</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5704317092895508</v>
+        <v>0.05027298629283905</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.09796179831027985</v>
+        <v>0.02004541084170341</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.1475883424282074</v>
+        <v>0.00768684409558773</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1943859308958054</v>
+        <v>0.04495175927877426</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.01421205699443817</v>
+        <v>0.05035093426704407</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.06115903332829475</v>
+        <v>0.01250021904706955</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.07050254195928574</v>
+        <v>0.01679729856550694</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.2068472653627396</v>
+        <v>0.06975238025188446</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0177542045712471</v>
+        <v>0.00413654837757349</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0018719881772995</v>
+        <v>0.02802471816539764</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.3283673524856567</v>
+        <v>0.01401885878294706</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.6257016062736511</v>
+        <v>0.0001915064640343189</v>
       </c>
       <c r="BV7" t="n">
-        <v>1.030783176422119</v>
+        <v>0.02045908384025097</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.1180292814970016</v>
+        <v>0.008044273592531681</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.6096962094306946</v>
+        <v>0.02559304796159267</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1500875651836395</v>
+        <v>0.01831980049610138</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.07187794148921967</v>
+        <v>0.03221986815333366</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.191119909286499</v>
+        <v>0.007068414706736803</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.08538775891065598</v>
+        <v>0.02667481452226639</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.6915097832679749</v>
+        <v>0.007920164614915848</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.129053145647049</v>
+        <v>0.001091498881578445</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.4078404903411865</v>
+        <v>0.06339530646800995</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.2666740119457245</v>
+        <v>0.02303347550332546</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.5106673836708069</v>
+        <v>0.05710934102535248</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.05158444494009018</v>
+        <v>0.01876816339790821</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.1949154436588287</v>
+        <v>0.00649248855188489</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.1749939471483231</v>
+        <v>0.001548990374431014</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0710182785987854</v>
+        <v>0.001616393215954304</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.2417715936899185</v>
+        <v>0.007889664731919765</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.4629846215248108</v>
+        <v>0.02921604551374912</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.2352189272642136</v>
+        <v>0.001823704689741135</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.1364315003156662</v>
+        <v>0.1153279095888138</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.11593858897686</v>
+        <v>0.119064599275589</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.2708298861980438</v>
+        <v>0.01798803545534611</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.3145043849945068</v>
+        <v>0.03612328693270683</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.505740761756897</v>
+        <v>0.0102715939283371</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.5485743284225464</v>
+        <v>0.01983663253486156</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.2797796130180359</v>
+        <v>0.002624467015266418</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.08886294811964035</v>
+        <v>0.0002566839102655649</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.3744194507598877</v>
+        <v>0.06421110033988953</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.3394621312618256</v>
+        <v>0.02287798933684826</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.5846533179283142</v>
+        <v>0.05549592524766922</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.06665963679552078</v>
+        <v>0.01887181773781776</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.2520275413990021</v>
+        <v>0.02086548134684563</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.1825084090232849</v>
+        <v>0.005987424403429031</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.1628188043832779</v>
+        <v>0.001462327316403389</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.04779697954654694</v>
+        <v>0.004486917518079281</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.03335963189601898</v>
+        <v>0.01259310357272625</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.5003634095191956</v>
+        <v>0.002929269336163998</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.03369112312793732</v>
+        <v>0.0007653282955288887</v>
       </c>
       <c r="DH7" t="n">
-        <v>1.12711763381958</v>
+        <v>0.01417654566466808</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01513113081455231</v>
+        <v>0.03078113496303558</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.2946439981460571</v>
+        <v>0.02816373854875565</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.2119122296571732</v>
+        <v>0.003640436567366123</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.2345514893531799</v>
+        <v>0.006557434797286987</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.01368457078933716</v>
+        <v>0.00945909321308136</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.2906821370124817</v>
+        <v>0.01049227081239223</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.1468620449304581</v>
+        <v>0.001102091744542122</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.2330073863267899</v>
+        <v>0.00722785945981741</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.2716023921966553</v>
+        <v>0.01184029318392277</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.1752637624740601</v>
+        <v>0.01404635794460773</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.5450092554092407</v>
+        <v>0.01433570683002472</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.253435879945755</v>
+        <v>0.01151229254901409</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.3601758480072021</v>
+        <v>0.02149642445147038</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.4861542582511902</v>
+        <v>0.02098727412521839</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.02971622347831726</v>
+        <v>0.005429182201623917</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.002241905778646469</v>
+        <v>0.02590452320873737</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.2718088924884796</v>
+        <v>0.0001191850751638412</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.5276407599449158</v>
+        <v>0.03459367901086807</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.2006934136152267</v>
+        <v>0.01630749739706516</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.08115631341934204</v>
+        <v>0.01553888525813818</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.2826363444328308</v>
+        <v>0.00369884492829442</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.1389901340007782</v>
+        <v>0.05995737016201019</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.07103411108255386</v>
+        <v>0.05516619607806206</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.2133667469024658</v>
+        <v>0.04078382253646851</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.4280561804771423</v>
+        <v>0.09343200922012329</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.3936914801597595</v>
+        <v>0.01653852313756943</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.1524674296379089</v>
+        <v>0.0696362629532814</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.1785210072994232</v>
+        <v>0.002277332358062267</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.393167108297348</v>
+        <v>0.007046207785606384</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.01352978311479092</v>
+        <v>0.01008459087461233</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.05760744959115982</v>
+        <v>0.003607509890571237</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.1026621833443642</v>
+        <v>0.0105294631794095</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.1638308465480804</v>
+        <v>0.04510217905044556</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.01678166911005974</v>
+        <v>0.0775483176112175</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.3801107108592987</v>
+        <v>0.05432039499282837</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.1865968555212021</v>
+        <v>0.04348404332995415</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.1453256905078888</v>
+        <v>0.06869343668222427</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.9214286208152771</v>
+        <v>0.03718523308634758</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.375362902879715</v>
+        <v>0.02380160987377167</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.4177501797676086</v>
+        <v>0.01149924099445343</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.1023534834384918</v>
+        <v>0.001081259921193123</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.07543055713176727</v>
+        <v>0.005031753797084093</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.3958570957183838</v>
+        <v>0.05184155702590942</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.2593251466751099</v>
+        <v>0.02097128517925739</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.5832188129425049</v>
+        <v>0.06605949997901917</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.04580648243427277</v>
+        <v>0.01686950214207172</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.2115941941738129</v>
+        <v>0.003433704609051347</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.2305251508951187</v>
+        <v>0.00485506234690547</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.1036828309297562</v>
+        <v>0.003802680876106024</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.1736175864934921</v>
+        <v>0.003575575072318316</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0984974205493927</v>
+        <v>0.004661294631659985</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.6797709465026855</v>
+        <v>0.008798131719231606</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.03197872266173363</v>
+        <v>0.02201450243592262</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.2966077923774719</v>
+        <v>0.0251389816403389</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.05268620699644089</v>
+        <v>0.04671740159392357</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.08385327458381653</v>
+        <v>0.03026740625500679</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.1363181620836258</v>
+        <v>0.005434541963040829</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.2106659412384033</v>
+        <v>0.02985774353146553</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.1263168156147003</v>
+        <v>0.007591442205011845</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.01584357395768166</v>
+        <v>0.01692217215895653</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.693569004535675</v>
+        <v>0.1016695722937584</v>
       </c>
       <c r="FR7" t="n">
-        <v>1.1628737449646</v>
+        <v>0.02037550508975983</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.3219279944896698</v>
+        <v>0.05802047997713089</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.1574132591485977</v>
+        <v>0.03044207766652107</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.4562654495239258</v>
+        <v>0.05359417200088501</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.3278487920761108</v>
+        <v>0.006437156349420547</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.5405126810073853</v>
+        <v>0.03475608304142952</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.07290014624595642</v>
+        <v>0.003767281770706177</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.2662979364395142</v>
+        <v>0.02338033355772495</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.2140694856643677</v>
+        <v>0.02413257770240307</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.1738170683383942</v>
+        <v>0.05694050341844559</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.05864038318395615</v>
+        <v>0.04888703674077988</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.7117180228233337</v>
+        <v>0.05923513695597649</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.1880447119474411</v>
+        <v>0.01697879284620285</v>
       </c>
       <c r="GE7" t="n">
-        <v>1.606816172599792</v>
+        <v>0.05446799471974373</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.4917978048324585</v>
+        <v>0.009351008571684361</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.4331567287445068</v>
+        <v>0.01527459267526865</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.08017878234386444</v>
+        <v>0.1029297858476639</v>
       </c>
       <c r="B8" t="n">
-        <v>0.449127733707428</v>
+        <v>0.4252831339836121</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01793969236314297</v>
+        <v>0.1910642683506012</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4200383126735687</v>
+        <v>0.05234850198030472</v>
       </c>
       <c r="E8" t="n">
-        <v>0.103262223303318</v>
+        <v>0.106927365064621</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01012858282774687</v>
+        <v>0.769120454788208</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008633587509393692</v>
+        <v>0.09120052307844162</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03609186410903931</v>
+        <v>0.1399092674255371</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009112155064940453</v>
+        <v>0.09436578303575516</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06676765531301498</v>
+        <v>0.05451461672782898</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3800450265407562</v>
+        <v>0.3735957145690918</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02450728416442871</v>
+        <v>0.2823646068572998</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2619701325893402</v>
+        <v>0.006167780607938766</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1195585429668427</v>
+        <v>0.08924201130867004</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02711650356650352</v>
+        <v>0.8099275827407837</v>
       </c>
       <c r="P8" t="n">
-        <v>0.06174907833337784</v>
+        <v>0.1805749833583832</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.05346590280532837</v>
+        <v>0.1631848812103271</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01303541474044323</v>
+        <v>0.1158352196216583</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03017128631472588</v>
+        <v>0.03188831359148026</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08241889625787735</v>
+        <v>0.0768086165189743</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01476344652473927</v>
+        <v>0.1034869700670242</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0206085778772831</v>
+        <v>0.01265064720064402</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01095505896955729</v>
+        <v>0.00979982316493988</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02258767560124397</v>
+        <v>0.1144032552838326</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.09403799474239349</v>
+        <v>0.07576213777065277</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03492719680070877</v>
+        <v>0.08258235454559326</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02657734602689743</v>
+        <v>0.05092347413301468</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.05699163675308228</v>
+        <v>0.1583527326583862</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.09309337288141251</v>
+        <v>0.123390406370163</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.005273604765534401</v>
+        <v>0.06534955650568008</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01254130806773901</v>
+        <v>0.1674270778894424</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.005645900499075651</v>
+        <v>0.2375935018062592</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0568428635597229</v>
+        <v>0.2663990557193756</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0103185772895813</v>
+        <v>0.0266110822558403</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.03194694221019745</v>
+        <v>0.3627667725086212</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001275912392884493</v>
+        <v>0.02972282469272614</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01714784279465675</v>
+        <v>0.03888268768787384</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.05143424868583679</v>
+        <v>0.2025706470012665</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.007494598627090454</v>
+        <v>0.09542199969291687</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.03160993382334709</v>
+        <v>0.03324816003441811</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.02897973172366619</v>
+        <v>0.07348868250846863</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.07185452431440353</v>
+        <v>0.08373954147100449</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.03557832539081573</v>
+        <v>0.02308057993650436</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.004056640900671482</v>
+        <v>0.06345206499099731</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.02251669019460678</v>
+        <v>0.07374304533004761</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.1224672496318817</v>
+        <v>0.02759217470884323</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.3302565813064575</v>
+        <v>0.2688320279121399</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.009169834665954113</v>
+        <v>0.2586157321929932</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.180634394288063</v>
+        <v>0.02204164490103722</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.05165934935212135</v>
+        <v>0.4320555329322815</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.01863632723689079</v>
+        <v>0.5373731851577759</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.08294641971588135</v>
+        <v>0.06091557815670967</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.03975867852568626</v>
+        <v>0.05550703033804893</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.940689101815224e-05</v>
+        <v>0.01353257149457932</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.004711393266916275</v>
+        <v>0.05679761245846748</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.08901551365852356</v>
+        <v>0.04492572322487831</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.007198506034910679</v>
+        <v>0.1416003108024597</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0335165336728096</v>
+        <v>0.06174571067094803</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.08118952810764313</v>
+        <v>0.02473621815443039</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.02597260475158691</v>
+        <v>0.01648017391562462</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.08291299641132355</v>
+        <v>0.0297793410718441</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.07231409847736359</v>
+        <v>0.07340504974126816</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.01724916324019432</v>
+        <v>0.05902935191988945</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.04139447212219238</v>
+        <v>0.02200758829712868</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.08504367619752884</v>
+        <v>0.008202701807022095</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.02137234807014465</v>
+        <v>0.008693408221006393</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.003826630301773548</v>
+        <v>0.008775552734732628</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.08107922971248627</v>
+        <v>0.03502644971013069</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.05423855036497116</v>
+        <v>0.04016237333416939</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.05624603480100632</v>
+        <v>0.0146927610039711</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.01495656091719866</v>
+        <v>0.02498956210911274</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.02392534911632538</v>
+        <v>0.1633870303630829</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.07208634912967682</v>
+        <v>0.002799242734909058</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1585314720869064</v>
+        <v>0.2114455848932266</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.05316329374909401</v>
+        <v>0.1059581339359283</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.03046465665102005</v>
+        <v>0.04299409314990044</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.009793216362595558</v>
+        <v>0.04992024600505829</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.004388210829347372</v>
+        <v>0.3469738364219666</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.00463831564411521</v>
+        <v>0.1019743978977203</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.03045135922729969</v>
+        <v>0.07253438979387283</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.02039769850671291</v>
+        <v>0.0418771505355835</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.002198851900175214</v>
+        <v>0.0001122700050473213</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0690143033862114</v>
+        <v>0.1601751744747162</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.006504771299660206</v>
+        <v>0.02212534472346306</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.04525585100054741</v>
+        <v>0.02128508500754833</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.005235655233263969</v>
+        <v>0.02914364263415337</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.00353184062987566</v>
+        <v>0.1756299138069153</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.013141886331141</v>
+        <v>0.004319168627262115</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.01708798855543137</v>
+        <v>0.1026804968714714</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.007170795928686857</v>
+        <v>0.07606007903814316</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.08891280740499496</v>
+        <v>0.03837045654654503</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.04311653971672058</v>
+        <v>0.0701206848025322</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.002273701131343842</v>
+        <v>0.2464644312858582</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.1427710354328156</v>
+        <v>0.2399580925703049</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.1501152068376541</v>
+        <v>0.3318617343902588</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.03613604977726936</v>
+        <v>0.03809283673763275</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.03240899741649628</v>
+        <v>5.635805428028107e-05</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.137628898024559</v>
+        <v>0.09943749010562897</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.00664188526570797</v>
+        <v>0.1095201075077057</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.002105657011270523</v>
+        <v>0.01067803427577019</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.06899809092283249</v>
+        <v>0.1255259215831757</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.01898637600243092</v>
+        <v>0.04804595559835434</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.07423227280378342</v>
+        <v>0.01485782489180565</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.01416600961238146</v>
+        <v>0.02941712737083435</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.01734483428299427</v>
+        <v>0.1884269118309021</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.006326998583972454</v>
+        <v>0.006836413405835629</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.009008192457258701</v>
+        <v>0.09198100864887238</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.00424785865470767</v>
+        <v>0.04838376119732857</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.02640062943100929</v>
+        <v>0.1300596743822098</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.07403260469436646</v>
+        <v>0.1319554001092911</v>
       </c>
       <c r="DG8" t="n">
-        <v>7.895240560173988e-05</v>
+        <v>0.1093407943844795</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.1926335990428925</v>
+        <v>0.1299336105585098</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01563367620110512</v>
+        <v>0.2122723162174225</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.03453922271728516</v>
+        <v>0.4026951193809509</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.01085406262427568</v>
+        <v>0.02876627445220947</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.1018848195672035</v>
+        <v>0.1415679305791855</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.01916597597301006</v>
+        <v>0.07347527891397476</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.01553161814808846</v>
+        <v>0.04275871813297272</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.06622064113616943</v>
+        <v>0.1010064259171486</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.02112104743719101</v>
+        <v>0.03009690903127193</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0894518718123436</v>
+        <v>0.06098220869898796</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01484276261180639</v>
+        <v>0.01114597544074059</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.04992906004190445</v>
+        <v>0.007005138788372278</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.02216727659106255</v>
+        <v>0.05238447338342667</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.001547375810332596</v>
+        <v>0.07684288918972015</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.02156732976436615</v>
+        <v>0.09792400151491165</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.007662628777325153</v>
+        <v>0.0456201583147049</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.02627759054303169</v>
+        <v>0.01649874821305275</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.02863155119121075</v>
+        <v>0.1840173602104187</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.003701827023178339</v>
+        <v>0.04680696129798889</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.04365235939621925</v>
+        <v>0.04831923544406891</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.024669224396348</v>
+        <v>0.003418391570448875</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.04310004413127899</v>
+        <v>0.01037856563925743</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.008455503731966019</v>
+        <v>0.2043258249759674</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.001605764962732792</v>
+        <v>0.2844516336917877</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.009255639277398586</v>
+        <v>0.01056548953056335</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.056321170181036</v>
+        <v>0.04602194204926491</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.01368850655853748</v>
+        <v>0.08640162646770477</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.1420111209154129</v>
+        <v>0.001396654173731804</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.09909579902887344</v>
+        <v>0.02863172069191933</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0172717310488224</v>
+        <v>0.08284252136945724</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.02396903373301029</v>
+        <v>0.01231452263891697</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0003701304085552692</v>
+        <v>0.008966663852334023</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.008778887800872326</v>
+        <v>0.02526655234396458</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.06253604590892792</v>
+        <v>0.01923450455069542</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.03589174896478653</v>
+        <v>0.1414923965930939</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.01665918342769146</v>
+        <v>0.04964432865381241</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.04605628922581673</v>
+        <v>0.006969836074858904</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.05270304158329964</v>
+        <v>0.07994262129068375</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.02520174719393253</v>
+        <v>0.1060605049133301</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.006935724057257175</v>
+        <v>0.0007341578602790833</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.01164771988987923</v>
+        <v>0.01022008061408997</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.01690514385700226</v>
+        <v>0.04775593802332878</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.02284295111894608</v>
+        <v>0.009705474600195885</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.06229598447680473</v>
+        <v>0.1516180038452148</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.009076489135622978</v>
+        <v>0.03879237920045853</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.05837744846940041</v>
+        <v>0.03078081645071507</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0135305542498827</v>
+        <v>0.007742376998066902</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.02377122081816196</v>
+        <v>0.1661352813243866</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.007606608793139458</v>
+        <v>0.003432797733694315</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.01197093073278666</v>
+        <v>0.0597374364733696</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.008856848813593388</v>
+        <v>0.001141698914580047</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.007584372069686651</v>
+        <v>0.01144428178668022</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0287668239325285</v>
+        <v>0.0900437980890274</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.03629841655492783</v>
+        <v>0.1348711103200912</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.08927307277917862</v>
+        <v>0.06940072774887085</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0438494049012661</v>
+        <v>0.05239197611808777</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.01243157126009464</v>
+        <v>0.3357412815093994</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.08107148110866547</v>
+        <v>0.0634893923997879</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.00250167865306139</v>
+        <v>0.1556313782930374</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.01680765300989151</v>
+        <v>0.3399345278739929</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.09151423722505569</v>
+        <v>0.08909440040588379</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.04051901400089264</v>
+        <v>0.1117203384637833</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.008009713143110275</v>
+        <v>0.247314527630806</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.07684309035539627</v>
+        <v>0.00379602238535881</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.1191385611891747</v>
+        <v>0.02007921971380711</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.02532380074262619</v>
+        <v>0.2756344974040985</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.01698929443955421</v>
+        <v>0.03163072466850281</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.02390310540795326</v>
+        <v>0.4500160217285156</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.02430029027163982</v>
+        <v>0.1061841323971748</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.1095998361706734</v>
+        <v>0.06634677946567535</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.02681804448366165</v>
+        <v>0.01259193941950798</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.006863150745630264</v>
+        <v>0.1742964088916779</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0001866975799202919</v>
+        <v>0.0131252259016037</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0457116886973381</v>
+        <v>0.3852970004081726</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.07031445205211639</v>
+        <v>0.2162927985191345</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.07637530565261841</v>
+        <v>0.0489557757973671</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.009797943755984306</v>
+        <v>0.02281899563968182</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.02490544132888317</v>
+        <v>0.01422650367021561</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.3113335072994232</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1023179739713669</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3949578702449799</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1301283836364746</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2241294980049133</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02220671251416206</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001658696681261063</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1068326830863953</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05927734076976776</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1667966693639755</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06314938515424728</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2808319628238678</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2159008383750916</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1770388931035995</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1440646052360535</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.04909507557749748</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03007538057863712</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1396859586238861</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.007564477622509003</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0764077752828598</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1327645629644394</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06248504668474197</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.09976606070995331</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.08108151704072952</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03145784884691238</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02536420710384846</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02233081124722958</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03921384364366531</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0270631555467844</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.1398031115531921</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.04802834987640381</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.03834264725446701</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.05705685913562775</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.02520025707781315</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.02701390162110329</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.04147472232580185</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.07844165712594986</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1820544898509979</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.07806181907653809</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.03403271734714508</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.04258165135979652</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.08030508458614349</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.06889322400093079</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.06192513182759285</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0645131915807724</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.2013227045536041</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.156440868973732</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2818787395954132</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0819348469376564</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.481297105550766</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.05147366598248482</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1441210210323334</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2178949266672134</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.08989658951759338</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.06999477744102478</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.3087993860244751</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.03687188401818275</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.2713238596916199</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.01383083313703537</v>
+        <v>0</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.2293390929698944</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.03955624252557755</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.312242329120636</v>
+        <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0002412013709545135</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.1077395752072334</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.06550782173871994</v>
+        <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.1290172338485718</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.2523695826530457</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01892816834151745</v>
+        <v>0</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.1588680893182755</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.1351903527975082</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.03800009936094284</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.1912669539451599</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.05391143262386322</v>
+        <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.05198724940419197</v>
+        <v>0</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0889950692653656</v>
+        <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.09141169488430023</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.269407331943512</v>
+        <v>0</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.1287019550800323</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.08548513054847717</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.1399814039468765</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.1712377667427063</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.05050325021147728</v>
+        <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.01737559214234352</v>
+        <v>0</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.06400913000106812</v>
+        <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.07195139676332474</v>
+        <v>0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.03078392706811428</v>
+        <v>0</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.009695230051875114</v>
+        <v>0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.005148069467395544</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.01341861486434937</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.01164658740162849</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.05938837677240372</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.002306688576936722</v>
+        <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.02301051840186119</v>
+        <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.1339455991983414</v>
+        <v>0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.2851088345050812</v>
+        <v>0</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.07207021117210388</v>
+        <v>0</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.168090745806694</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.005498318001627922</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.104591891169548</v>
+        <v>0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0384458489716053</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.02090743370354176</v>
+        <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.07297255098819733</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.07759614288806915</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.02208499610424042</v>
+        <v>0</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.01737350970506668</v>
+        <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.01059523783624172</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.01625414565205574</v>
+        <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.00924965925514698</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.01016071438789368</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.26091268658638</v>
+        <v>0</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.2669397294521332</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1702378988265991</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.01443695649504662</v>
+        <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.1425428688526154</v>
+        <v>0</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.03693064302206039</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.001781441271305084</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.08204860240221024</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.02425285428762436</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.1199831813573837</v>
+        <v>0</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.02907351404428482</v>
+        <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.002914473414421082</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.06615083664655685</v>
+        <v>0</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.1054495722055435</v>
+        <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.04941166192293167</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.07336000353097916</v>
+        <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.1638117432594299</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.04409322515130043</v>
+        <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.09423346817493439</v>
+        <v>0</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.04117448627948761</v>
+        <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.1602167934179306</v>
+        <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.1847963184118271</v>
+        <v>0</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.154219850897789</v>
+        <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.004866697359830141</v>
+        <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.1757074147462845</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.02849391847848892</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.02347258105874062</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.1115012764930725</v>
+        <v>0</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.1600594222545624</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.08684859424829483</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.07236984372138977</v>
+        <v>0</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.04000517725944519</v>
+        <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0253637358546257</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.04995033144950867</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.08880393952131271</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.04212202131748199</v>
+        <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.09228252619504929</v>
+        <v>0</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.01499481033533812</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.05259016156196594</v>
+        <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.1110154241323471</v>
+        <v>0</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.07268624007701874</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.1425292491912842</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.07792740315198898</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.161596342921257</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0157475434243679</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.003007611259818077</v>
+        <v>0</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.06171311438083649</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.04230481386184692</v>
+        <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.02282630652189255</v>
+        <v>0</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.04589616507291794</v>
+        <v>0</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.01536216121166945</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.01250821631401777</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.02345491200685501</v>
+        <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.1519598811864853</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.1463440805673599</v>
+        <v>0</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.03427671641111374</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.03230224177241325</v>
+        <v>0</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.09513064473867416</v>
+        <v>0</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.06480347365140915</v>
+        <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.1067226007580757</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.04405622556805611</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.06131987273693085</v>
+        <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.1622417569160461</v>
+        <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.01413344219326973</v>
+        <v>0</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.07726531475782394</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.004420313984155655</v>
+        <v>0</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.03452059626579285</v>
+        <v>0</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.1303622722625732</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.1581957936286926</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.1494160890579224</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.09283928573131561</v>
+        <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.03567013889551163</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.158032700419426</v>
+        <v>0</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.03388994187116623</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.1894887238740921</v>
+        <v>0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.01576643064618111</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.1234583854675293</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.09426071494817734</v>
+        <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.04117321595549583</v>
+        <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.03499270603060722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0005043139681220055</v>
+        <v>0.008382963947951794</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1332651525735855</v>
+        <v>0.05162636190652847</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01490675751119852</v>
+        <v>0.02837004326283932</v>
       </c>
       <c r="D10" t="n">
-        <v>0.04002486914396286</v>
+        <v>0.04398133605718613</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01038746349513531</v>
+        <v>0.03328052908182144</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1381137520074844</v>
+        <v>0.1302896738052368</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005351878702640533</v>
+        <v>0.02756296284496784</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04572324082255363</v>
+        <v>0.05273216962814331</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002917067147791386</v>
+        <v>0.01782850548624992</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01903901249170303</v>
+        <v>0.02790470793843269</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1095054969191551</v>
+        <v>0.05853692442178726</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02709362283349037</v>
+        <v>0.0260625034570694</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04553962498903275</v>
+        <v>0.05363321304321289</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001300103031098843</v>
+        <v>0.03193605691194534</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1086322218179703</v>
+        <v>0.1420641541481018</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0005142055451869965</v>
+        <v>0.08080475032329559</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.03482170403003693</v>
+        <v>0.08510097861289978</v>
       </c>
       <c r="R10" t="n">
-        <v>0.02101024985313416</v>
+        <v>0.0343196839094162</v>
       </c>
       <c r="S10" t="n">
-        <v>0.004528379067778587</v>
+        <v>0.0261374618858099</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01281041279435158</v>
+        <v>0.03595597296953201</v>
       </c>
       <c r="U10" t="n">
-        <v>0.002193874679505825</v>
+        <v>0.003763125278055668</v>
       </c>
       <c r="V10" t="n">
-        <v>0.02236221544444561</v>
+        <v>0.049897450953722</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02055542729794979</v>
+        <v>0.007741434499621391</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01829849556088448</v>
+        <v>0.02650026604533195</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.003177684033289552</v>
+        <v>0.02749098464846611</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01461388915777206</v>
+        <v>0.04295435547828674</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.009320426732301712</v>
+        <v>0.0361204706132412</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.001293375971727073</v>
+        <v>0.004276685416698456</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.01606239378452301</v>
+        <v>3.608502447605133e-05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.01805520989000797</v>
+        <v>0.007424648851156235</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.01591635122895241</v>
+        <v>0.08578057587146759</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.003558361437171698</v>
+        <v>0.02072987891733646</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.003519265912473202</v>
+        <v>0.04242628067731857</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.009938065893948078</v>
+        <v>0.01402153261005878</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01056350860744715</v>
+        <v>0.07262521982192993</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.01630671694874763</v>
+        <v>0.02097373642027378</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0126253729686141</v>
+        <v>0.03215024620294571</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01390805840492249</v>
+        <v>0.04710614308714867</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.007062340155243874</v>
+        <v>0.004179822281002998</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.01326014194637537</v>
+        <v>0.02693280950188637</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.01243786793202162</v>
+        <v>0.04174318164587021</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.02726238593459129</v>
+        <v>0.008981152437627316</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.005485998932272196</v>
+        <v>0.003556505544111133</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.006416376680135727</v>
+        <v>0.03667549788951874</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.005882986821234226</v>
+        <v>0.0005072443746030331</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.01214784011244774</v>
+        <v>0.04978382587432861</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.08543220907449722</v>
+        <v>0.07563656568527222</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.007799576967954636</v>
+        <v>0.01565525680780411</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0201983992010355</v>
+        <v>0.01644048467278481</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.02177081629633904</v>
+        <v>0.02843993715941906</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.09666025638580322</v>
+        <v>0.08615399152040482</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0284571535885334</v>
+        <v>0.01978445611894131</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.01044963952153921</v>
+        <v>1.950189471244812e-06</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.02375307492911816</v>
+        <v>0.02838103473186493</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.00698043592274189</v>
+        <v>0.04768280312418938</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0455624908208847</v>
+        <v>0.03379788622260094</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0291280560195446</v>
+        <v>0.03351299464702606</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.02106060832738876</v>
+        <v>0.0323193334043026</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.009512281976640224</v>
+        <v>0.07663124054670334</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.03189035132527351</v>
+        <v>0.02367528155446053</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.02359277382493019</v>
+        <v>0.04882676526904106</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.006979325786232948</v>
+        <v>0.03816310316324234</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.01950255781412125</v>
+        <v>0.008101930841803551</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0006539965979754925</v>
+        <v>0.002803188748657703</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.02235814370214939</v>
+        <v>0.01132117956876755</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.00894565973430872</v>
+        <v>0.006508686579763889</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0001863597426563501</v>
+        <v>0.02887469343841076</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.01270096655935049</v>
+        <v>0.0368390753865242</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.00797694269567728</v>
+        <v>0.06773693859577179</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.003581108525395393</v>
+        <v>0.01880749128758907</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.004208918660879135</v>
+        <v>0.01394225377589464</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.02512798830866814</v>
+        <v>0.008663706481456757</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.006532236468046904</v>
+        <v>0.05476481840014458</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.04708876460790634</v>
+        <v>0.07342906296253204</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.004378649406135082</v>
+        <v>0.005100741051137447</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01433356106281281</v>
+        <v>0.03156798332929611</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01346852909773588</v>
+        <v>0.03639486059546471</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.04574213549494743</v>
+        <v>0.03532467037439346</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0005780658102594316</v>
+        <v>0.01881406828761101</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.009467285126447678</v>
+        <v>0.04094798490405083</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0001891606952995062</v>
+        <v>0.003568678162992001</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0003473563119769096</v>
+        <v>0.01395764015614986</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.01663209311664104</v>
+        <v>0.02372368797659874</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.006676311139017344</v>
+        <v>0.006149370223283768</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0009893167298287153</v>
+        <v>0.03022912703454494</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.002892082557082176</v>
+        <v>0.01435681246221066</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02493800595402718</v>
+        <v>0.03724722936749458</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.003744265995919704</v>
+        <v>0.005693108774721622</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.009563852101564407</v>
+        <v>0.004382316954433918</v>
       </c>
       <c r="CL10" t="n">
-        <v>4.690873902291059e-05</v>
+        <v>0.002414132934063673</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.01813825964927673</v>
+        <v>0.01278842985630035</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.01352534908801317</v>
+        <v>0.02832468971610069</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.00226917490363121</v>
+        <v>0.03930092975497246</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0007414300926029682</v>
+        <v>0.04835957661271095</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.01626798883080482</v>
+        <v>0.07987914234399796</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.01663843356072903</v>
+        <v>0.004645105451345444</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.001014386769384146</v>
+        <v>0.06562917679548264</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.01588453538715839</v>
+        <v>0.02860118821263313</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.01003102026879787</v>
+        <v>0.00585906021296978</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.004218298941850662</v>
+        <v>0.007535162381827831</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0140416007488966</v>
+        <v>0.01903960481286049</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.005188921932131052</v>
+        <v>0.01138484291732311</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.005978207103908062</v>
+        <v>0.02838830091059208</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.003117459360510111</v>
+        <v>0.006707204040139914</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.02320673502981663</v>
+        <v>0.03507273271679878</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0002483152784407139</v>
+        <v>0.009726019576191902</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.01207716390490532</v>
+        <v>0.01665463298559189</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.002502256538718939</v>
+        <v>0.001870391773991287</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.01563163660466671</v>
+        <v>0.006635798141360283</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.008302748203277588</v>
+        <v>0.03724132478237152</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.004584196954965591</v>
+        <v>0.004637640435248613</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.03744034469127655</v>
+        <v>0.04500304907560349</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.009670807048678398</v>
+        <v>0.05173744633793831</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.02466857805848122</v>
+        <v>0.01102072186768055</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.00371570372954011</v>
+        <v>0.02504619583487511</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.03420962393283844</v>
+        <v>0.04286820441484451</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.01843152195215225</v>
+        <v>0.106318861246109</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.004734002519398928</v>
+        <v>0.03518997877836227</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.006202070973813534</v>
+        <v>0.01399641763418913</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.01227433420717716</v>
+        <v>0.007804315071552992</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.01041694916784763</v>
+        <v>0.01962398365139961</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.005396401975303888</v>
+        <v>0.02603914588689804</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0162503756582737</v>
+        <v>0.0529048927128315</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.01091922447085381</v>
+        <v>0.001375326886773109</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.006549795158207417</v>
+        <v>0.02330245263874531</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.003956317901611328</v>
+        <v>0.01215359102934599</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.004280553665012121</v>
+        <v>0.002653844654560089</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.00476181274279952</v>
+        <v>0.04270352050662041</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.004321092739701271</v>
+        <v>0.02060410752892494</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.008065545931458473</v>
+        <v>0.01689478382468224</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.01606310904026031</v>
+        <v>0.03887243568897247</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.00288231554441154</v>
+        <v>0.01109048258513212</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.005773329176008701</v>
+        <v>0.01033773738890886</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.01619045436382294</v>
+        <v>0.002549859927967191</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.01389357820153236</v>
+        <v>0.007783223409205675</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.003475145203992724</v>
+        <v>0.0009551187977194786</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.01062976755201817</v>
+        <v>0.004236964043229818</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.004937898367643356</v>
+        <v>0.00671769306063652</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0159772764891386</v>
+        <v>0.02969006448984146</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.00105559453368187</v>
+        <v>0.03316287323832512</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.005378417670726776</v>
+        <v>0.02231510728597641</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.008884673938155174</v>
+        <v>0.03043916821479797</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.007757799234241247</v>
+        <v>0.01856451667845249</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.007065234240144491</v>
+        <v>0.01414347346872091</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.009492836892604828</v>
+        <v>0.005078325979411602</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.005655825138092041</v>
+        <v>0.01885970681905746</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.00172052625566721</v>
+        <v>0.00452035665512085</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.01540124882012606</v>
+        <v>0.0364406481385231</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.005113016813993454</v>
+        <v>0.03129051625728607</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.01486996933817863</v>
+        <v>0.0210607722401619</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.002755720168352127</v>
+        <v>0.02404354326426983</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.02487031370401382</v>
+        <v>0.03459404781460762</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.007563707884401083</v>
+        <v>0.05383789539337158</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.002731506712734699</v>
+        <v>0.01312368083745241</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.01400428451597691</v>
+        <v>0.02065292745828629</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.001577901188284159</v>
+        <v>0.008658905513584614</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0009537078440189362</v>
+        <v>0.02910491079092026</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.00596697861328721</v>
+        <v>0.02192584425210953</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.02121385931968689</v>
+        <v>0.02897295542061329</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.004327725619077682</v>
+        <v>0.01074348669499159</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.006020365282893181</v>
+        <v>0.02378307282924652</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0001263469457626343</v>
+        <v>0.01770622283220291</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.005431890487670898</v>
+        <v>0.009832911193370819</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.01260599680244923</v>
+        <v>0.01789676211774349</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.005427305586636066</v>
+        <v>0.003821598365902901</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.02523893117904663</v>
+        <v>0.02935673296451569</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.01705836318433285</v>
+        <v>0.01728159934282303</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.02766930311918259</v>
+        <v>0.01546577829867601</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.01059053000062704</v>
+        <v>0.00325322337448597</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.009353333152830601</v>
+        <v>0.009990977123379707</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.005676157772541046</v>
+        <v>0.001515189185738564</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.01463970541954041</v>
+        <v>0.02210670709609985</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.03391740098595619</v>
+        <v>0.02309350296854973</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.01235576998442411</v>
+        <v>0.0351807102560997</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.01763789355754852</v>
+        <v>0.0039801225066185</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.002654359210282564</v>
+        <v>0.03184423223137856</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.02666528150439262</v>
+        <v>0.008106745779514313</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.009788898751139641</v>
+        <v>0.008498881012201309</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.002825866919010878</v>
+        <v>0.009530885145068169</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.01596776582300663</v>
+        <v>0.0443287119269371</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.01697348989546299</v>
+        <v>0.0315658412873745</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.006424335762858391</v>
+        <v>0.0252285897731781</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.002674168907105923</v>
+        <v>0.04120393842458725</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.009273527190089226</v>
+        <v>0.05621359124779701</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.05534109473228455</v>
+        <v>0.04150911793112755</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.01459417399019003</v>
+        <v>0.03044433519244194</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.0204603411257267</v>
+        <v>0.00912749394774437</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.01277623232454062</v>
+        <v>0.01614323444664478</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.003068200312554836</v>
+        <v>0.003632307052612305</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0003756143851205707</v>
+        <v>0.1871585547924042</v>
       </c>
       <c r="B11" t="n">
-        <v>0.006826573982834816</v>
+        <v>0.4280132055282593</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000219050794839859</v>
+        <v>0.08728866279125214</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003506915178149939</v>
+        <v>0.0375460609793663</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002698406577110291</v>
+        <v>0.1052472367882729</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002715169684961438</v>
+        <v>0.1286095678806305</v>
       </c>
       <c r="G11" t="n">
-        <v>0.000410209788242355</v>
+        <v>0.0009261816740036011</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0004236467648297548</v>
+        <v>0.05282657593488693</v>
       </c>
       <c r="I11" t="n">
-        <v>9.70515247900039e-05</v>
+        <v>0.1901686042547226</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0002628452493809164</v>
+        <v>0.1438836306333542</v>
       </c>
       <c r="K11" t="n">
-        <v>0.005665552336722612</v>
+        <v>0.4993512034416199</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001143093686550856</v>
+        <v>0.103719174861908</v>
       </c>
       <c r="M11" t="n">
-        <v>0.004088514018803835</v>
+        <v>0.01157509349286556</v>
       </c>
       <c r="N11" t="n">
-        <v>0.004139592405408621</v>
+        <v>0.1850017160177231</v>
       </c>
       <c r="O11" t="n">
-        <v>0.00523726548999548</v>
+        <v>0.04426101595163345</v>
       </c>
       <c r="P11" t="n">
-        <v>0.002437406918033957</v>
+        <v>0.02865558676421642</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001728731556795537</v>
+        <v>0.02535310387611389</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0006551180849783123</v>
+        <v>0.1852873712778091</v>
       </c>
       <c r="S11" t="n">
-        <v>1.056031760526821e-05</v>
+        <v>0.01701590418815613</v>
       </c>
       <c r="T11" t="n">
-        <v>0.002618669532239437</v>
+        <v>0.0409572571516037</v>
       </c>
       <c r="U11" t="n">
-        <v>0.000900385610293597</v>
+        <v>0.02010787464678288</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001766992150805891</v>
+        <v>0.0644577294588089</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001647328725084662</v>
+        <v>0.09905079007148743</v>
       </c>
       <c r="X11" t="n">
-        <v>0.00166221137624234</v>
+        <v>0.08010579645633698</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0004959714715369046</v>
+        <v>0.02752462774515152</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0001504659012425691</v>
+        <v>0.00598515197634697</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.001214835559949279</v>
+        <v>0.1169385761022568</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.000441623036749661</v>
+        <v>0.1227918043732643</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.001859307056292892</v>
+        <v>0.01913772523403168</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0009127240628004074</v>
+        <v>0.02866607159376144</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.001252115122042596</v>
+        <v>0.08308841288089752</v>
       </c>
       <c r="AF11" t="n">
-        <v>7.792341057211161e-05</v>
+        <v>0.1390365064144135</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0004462833167053759</v>
+        <v>0.02937313728034496</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.002258351305499673</v>
+        <v>0.03644546866416931</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0008382449159398675</v>
+        <v>0.09795275330543518</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0003319043607916683</v>
+        <v>0.01664211042225361</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.001830107066780329</v>
+        <v>0.009988915175199509</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.001281441887840629</v>
+        <v>0.132050096988678</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0004279325075913221</v>
+        <v>0.08690451085567474</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0007162416586652398</v>
+        <v>0.03093034401535988</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.001362131792120636</v>
+        <v>0.02665937319397926</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0002866929862648249</v>
+        <v>0.02877160906791687</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0006357543752528727</v>
+        <v>0.01763813570141792</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.0001132854667957872</v>
+        <v>0.04613995552062988</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0004420194018166512</v>
+        <v>0.06392543017864227</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.002886825241148472</v>
+        <v>0.01218173652887344</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.00802470650523901</v>
+        <v>0.3536069691181183</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.00138940813485533</v>
+        <v>0.01955990865826607</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.001823941478505731</v>
+        <v>0.03394624590873718</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.001329444814473391</v>
+        <v>0.03792507201433182</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.00248619494959712</v>
+        <v>0.01996863074600697</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.0006150685367174447</v>
+        <v>0.01303016673773527</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.002584919333457947</v>
+        <v>0.05438782274723053</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0006970418617129326</v>
+        <v>0.09603013098239899</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0004985124105587602</v>
+        <v>0.07582823932170868</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.0007646391750313342</v>
+        <v>0.04812199622392654</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.002218615263700485</v>
+        <v>0.0863589346408844</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.001716588390991092</v>
+        <v>0.01862126775085926</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.004484527744352818</v>
+        <v>0.01387352496385574</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.001491799717769027</v>
+        <v>0.09558892995119095</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.001059900969266891</v>
+        <v>0.07310675084590912</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.004229825455695391</v>
+        <v>0.08168432116508484</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0005440371460281312</v>
+        <v>0.05135649442672729</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.0007375844288617373</v>
+        <v>0.02214714139699936</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.003467333735898137</v>
+        <v>0.07302899658679962</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0005507808527909219</v>
+        <v>0.01665407605469227</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.002994635608047247</v>
+        <v>0.06461161375045776</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.004363242536783218</v>
+        <v>0.1375695466995239</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.000967719592154026</v>
+        <v>0.03916185721755028</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.001705263159237802</v>
+        <v>0.06825698912143707</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.0007255171076394618</v>
+        <v>0.06853347271680832</v>
       </c>
       <c r="BT11" t="n">
-        <v>9.068479994311929e-05</v>
+        <v>0.02827193215489388</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0006899626459926367</v>
+        <v>0.04637347906827927</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.003924176562577486</v>
+        <v>0.2291393578052521</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.0001309365907218307</v>
+        <v>0.01529757119715214</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0001867071841843426</v>
+        <v>0.03831302002072334</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0007224270375445485</v>
+        <v>0.08288951963186264</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.736117261927575e-05</v>
+        <v>0.1184290796518326</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.002315844874829054</v>
+        <v>0.03329261019825935</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.001231659669429064</v>
+        <v>0.0520058199763298</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0004572845064103603</v>
+        <v>0.1423489600419998</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0004164698184467852</v>
+        <v>0.07747325301170349</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.001554201007820666</v>
+        <v>0.1177759915590286</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0004086863191332668</v>
+        <v>0.02595704793930054</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.000870519841555506</v>
+        <v>0.01055311970412731</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0004627951420843601</v>
+        <v>0.01293162442743778</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0005905590951442719</v>
+        <v>0.06970375031232834</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.0002805307158268988</v>
+        <v>0.01939772814512253</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0002607665373943746</v>
+        <v>0.005001709796488285</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0001022089418256655</v>
+        <v>0.03467729315161705</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.003177868667989969</v>
+        <v>0.01986770331859589</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.003708950476720929</v>
+        <v>0.2392213046550751</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0001667413162067533</v>
+        <v>0.06949073076248169</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.002037419704720378</v>
+        <v>0.08256177604198456</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.001987373223528266</v>
+        <v>0.0346708670258522</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.0001319569419138134</v>
+        <v>0.154687225818634</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0005943641881458461</v>
+        <v>0.03946332633495331</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.0009973860578611493</v>
+        <v>0.003827976994216442</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0007440277840942144</v>
+        <v>0.0803060382604599</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0003569571999832988</v>
+        <v>0.05123128741979599</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.0009513595141470432</v>
+        <v>0.1057294309139252</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0005619900766760111</v>
+        <v>0.0205144714564085</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.001448936527594924</v>
+        <v>0.007628328166902065</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0002183321776101366</v>
+        <v>0.01902369223535061</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0004972144961357117</v>
+        <v>0.06426217406988144</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0007799785234965384</v>
+        <v>0.01982588320970535</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.001043768366798759</v>
+        <v>0.0004982259124517441</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.289480132982135e-05</v>
+        <v>0.04366075992584229</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.00191701645962894</v>
+        <v>0.01621360704302788</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.004128212109208107</v>
+        <v>0.1344477236270905</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.001030732179060578</v>
+        <v>0.01021367963403463</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.002973604016005993</v>
+        <v>0.02762079983949661</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.001877581933513284</v>
+        <v>0.09628846496343613</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0004367324872873724</v>
+        <v>0.08817637711763382</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.002842250978574157</v>
+        <v>0.01931259036064148</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.001291693886741996</v>
+        <v>0.05316206812858582</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.001305970828980207</v>
+        <v>0.121347039937973</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.0005431316094473004</v>
+        <v>0.03788316249847412</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.001199346268549562</v>
+        <v>0.05720575898885727</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.001507555251009762</v>
+        <v>0.03686555847525597</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0006821159622631967</v>
+        <v>0.002722839126363397</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.001449394854716957</v>
+        <v>0.0003816299140453339</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0009706910350359976</v>
+        <v>0.005260176956653595</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.000899611331988126</v>
+        <v>0.01303967460989952</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0004295666294638067</v>
+        <v>0.0645848736166954</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0002502430870663375</v>
+        <v>0.02653000503778458</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0004453864821698517</v>
+        <v>0.05187809094786644</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0002419279771856964</v>
+        <v>0.03034364432096481</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.001239013974554837</v>
+        <v>0.00237767118960619</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.001513163791969419</v>
+        <v>0.005784415639936924</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0006968075758777559</v>
+        <v>0.02820806950330734</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0001861707132775337</v>
+        <v>0.06681028008460999</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0004422257479745895</v>
+        <v>0.04035622999072075</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0004036977479699999</v>
+        <v>0.1292578428983688</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.0009068772196769714</v>
+        <v>0.04857468605041504</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.00126230507157743</v>
+        <v>0.04202038794755936</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0007323193713091314</v>
+        <v>0.03429973870515823</v>
       </c>
       <c r="EH11" t="n">
-        <v>4.796728171641007e-05</v>
+        <v>0.008394206874072552</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0009380832780152559</v>
+        <v>0.02942916937172413</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0001882753131212667</v>
+        <v>0.01834965497255325</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0002176272973883897</v>
+        <v>0.0905730351805687</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0008927431190386415</v>
+        <v>0.03582998737692833</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.000291006697807461</v>
+        <v>0.001020669471472502</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0001454457233194262</v>
+        <v>0.06744348257780075</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.001394988736137748</v>
+        <v>0.06776227802038193</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0005101441056467593</v>
+        <v>0.1066559553146362</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0008309271070174873</v>
+        <v>0.02494854480028152</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0003645380493253469</v>
+        <v>0.000143623910844326</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.0003990707919001579</v>
+        <v>0.03823084384202957</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0002511373604647815</v>
+        <v>0.07731318473815918</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.0007856368902139366</v>
+        <v>0.005193490535020828</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.001271406770683825</v>
+        <v>0.005969627760350704</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0004675303352996707</v>
+        <v>0.0001470781862735748</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0001314776018261909</v>
+        <v>0.07934687286615372</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0007317421259358525</v>
+        <v>0.1393115222454071</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0002665619249455631</v>
+        <v>0.03351215645670891</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0006590617122128606</v>
+        <v>0.01457808259874582</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0002567599003668875</v>
+        <v>0.003079188754782081</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0006637499900534749</v>
+        <v>0.06953520327806473</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.0005217139259912074</v>
+        <v>0.0252513624727726</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.0001790516980690882</v>
+        <v>0.007277894765138626</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0003196893667336553</v>
+        <v>0.05836595594882965</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.00144678819924593</v>
+        <v>0.0008458700031042099</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.001282373792491853</v>
+        <v>0.1317896842956543</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.00189221790060401</v>
+        <v>0.01234963070601225</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.000421327946241945</v>
+        <v>0.07246170938014984</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0005699261091649532</v>
+        <v>0.01717754825949669</v>
       </c>
       <c r="FL11" t="n">
-        <v>5.734302976634353e-05</v>
+        <v>0.002032589167356491</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.0005633403779938817</v>
+        <v>0.0446171797811985</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.000801779970061034</v>
+        <v>0.006449280306696892</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0002681280893739313</v>
+        <v>0.008477967232465744</v>
       </c>
       <c r="FP11" t="n">
-        <v>8.360180072486401e-05</v>
+        <v>0.02375435084104538</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0003000234719365835</v>
+        <v>0.09948486834764481</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.0004577163781505078</v>
+        <v>0.0940137580037117</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.00287738861516118</v>
+        <v>0.07575386017560959</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.004106746520847082</v>
+        <v>0.1328206658363342</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.0002386929409112781</v>
+        <v>0.1159546971321106</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.000659424695186317</v>
+        <v>0.02973202243447304</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.002541920635849237</v>
+        <v>0.04068974405527115</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0002472384367138147</v>
+        <v>0.04820601642131805</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.001327981008216739</v>
+        <v>0.08334735035896301</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.001774442382156849</v>
+        <v>0.05579686909914017</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0001871963031589985</v>
+        <v>0.008379025384783745</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.002880624029785395</v>
+        <v>0.03308673202991486</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0006050095544196665</v>
+        <v>0.1109100505709648</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.0005659881280735135</v>
+        <v>0.107878640294075</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.002891086507588625</v>
+        <v>0.01818307302892208</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.001852330751717091</v>
+        <v>0.07880530506372452</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.001569980289787054</v>
+        <v>0.1411919295787811</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8.766460814513266e-05</v>
+        <v>0.0005678310990333557</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001786738284863532</v>
+        <v>0.001932877348735929</v>
       </c>
       <c r="C12" t="n">
-        <v>9.870631038211286e-05</v>
+        <v>0.0004146050778217614</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001039296388626099</v>
+        <v>0.001553609617985785</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0003799956466536969</v>
+        <v>8.702705963514745e-05</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0004726718179881573</v>
+        <v>0.001480063539929688</v>
       </c>
       <c r="G12" t="n">
-        <v>4.473273293115199e-05</v>
+        <v>0.0005380820366553962</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0002200023009208962</v>
+        <v>0.0004229086334817111</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0001451318676117808</v>
+        <v>0.0003025144687853754</v>
       </c>
       <c r="J12" t="n">
-        <v>2.252677222713828e-05</v>
+        <v>0.0006071245297789574</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001342330244369805</v>
+        <v>0.002077062614262104</v>
       </c>
       <c r="L12" t="n">
-        <v>3.66157473763451e-05</v>
+        <v>0.0007728826603852212</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0008630123338662088</v>
+        <v>0.002048157155513763</v>
       </c>
       <c r="N12" t="n">
-        <v>0.00032248449861072</v>
+        <v>0.0004187870363239199</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0004830031248275191</v>
+        <v>0.001288194209337234</v>
       </c>
       <c r="P12" t="n">
-        <v>1.603603595867753e-05</v>
+        <v>0.0003981132467743009</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0001450210984330624</v>
+        <v>4.792342224391177e-05</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0003341247502248734</v>
+        <v>0.0002253036363981664</v>
       </c>
       <c r="S12" t="n">
-        <v>7.377841393463314e-05</v>
+        <v>0.0001453164441045374</v>
       </c>
       <c r="T12" t="n">
-        <v>0.000127586186863482</v>
+        <v>7.46322184568271e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0002618432627059519</v>
+        <v>0.0001253365771844983</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0003727749863173813</v>
+        <v>6.22191873844713e-05</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0001894715533126146</v>
+        <v>8.352253644261509e-06</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0002019602688960731</v>
+        <v>0.0006493220571428537</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.8057587769581e-05</v>
+        <v>0.0001044145610649139</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0001002678327495232</v>
+        <v>0.000276286416919902</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.034167871694081e-05</v>
+        <v>0.0002426204737275839</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.828044570283964e-05</v>
+        <v>0.0003318630624562502</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.125990330474451e-05</v>
+        <v>0.0003419495769776404</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0002857870131265372</v>
+        <v>0.0002672799455467612</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0004278169653844088</v>
+        <v>4.414658178575337e-05</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.89620365947485e-05</v>
+        <v>1.080723450286314e-05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0004093866446055472</v>
+        <v>0.0005987510085105896</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.786562279448844e-05</v>
+        <v>0.0001228343753609806</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0002559603308327496</v>
+        <v>0.0002789489517454058</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0003437657142058015</v>
+        <v>0.0002435849164612591</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0001291898952331394</v>
+        <v>6.118489545769989e-05</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0001815228315535933</v>
+        <v>0.0006115297437645495</v>
       </c>
       <c r="AM12" t="n">
-        <v>4.348466609371826e-05</v>
+        <v>0.0002620463201310486</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.115586878266186e-06</v>
+        <v>0.0003610170097090304</v>
       </c>
       <c r="AO12" t="n">
-        <v>3.876977280015126e-05</v>
+        <v>0.000395969080273062</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0002666341897565871</v>
+        <v>0.0003612094442360103</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0001271821529371664</v>
+        <v>0.0002226080832770094</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.521768328733742e-05</v>
+        <v>0.0001542798854643479</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.048649422358721e-05</v>
+        <v>0.0002271771227242425</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0001008178805932403</v>
+        <v>2.530342317186296e-05</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.001062760245986283</v>
+        <v>0.001546935178339481</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.0001063664822140709</v>
+        <v>0.0001308168866671622</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.398225403041579e-05</v>
+        <v>0.001054126187227666</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0001542518002679572</v>
+        <v>0.0005043621640652418</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0001817148004192859</v>
+        <v>0.0008093713549897075</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.0002767693367786705</v>
+        <v>8.015005005290732e-05</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0002390206063864753</v>
+        <v>8.889806485967711e-05</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.453320485074073e-05</v>
+        <v>0.0001718190760584548</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.923676245496608e-05</v>
+        <v>0.0004978147917427123</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0002089165354846045</v>
+        <v>0.0003533440176397562</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0003682398237287998</v>
+        <v>0.0004150312743149698</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0007445885566994548</v>
+        <v>0.0002713112044148147</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.0005087887984700501</v>
+        <v>0.0002659983292687684</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0003364691801834852</v>
+        <v>0.0001099417713703588</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0003919337468687445</v>
+        <v>0.0001763807667884976</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0001887865655589849</v>
+        <v>0.0001076708576874807</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.127545278402977e-05</v>
+        <v>0.0003155091253574938</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0003718839725479484</v>
+        <v>0.0002582864253781736</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0001260703720618039</v>
+        <v>0.0001679012493696064</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0001075929976650514</v>
+        <v>1.96881501324242e-06</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0002519631816539913</v>
+        <v>0.0002523091097828001</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0002261994668515399</v>
+        <v>0.0002332205476704985</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0001449475530534983</v>
+        <v>0.0002485864970367402</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0002375594631303102</v>
+        <v>8.875709681888111e-06</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.559964120038785e-05</v>
+        <v>0.0002690904366318136</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.0001235524250660092</v>
+        <v>0.0001086482661776245</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0001406888623023406</v>
+        <v>2.440816024318337e-05</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.000739903945941478</v>
+        <v>0.0008409748552367091</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.471930878935382e-05</v>
+        <v>8.990929927676916e-05</v>
       </c>
       <c r="BX12" t="n">
-        <v>9.386540477862582e-05</v>
+        <v>0.000882580759935081</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.070681694021914e-05</v>
+        <v>0.0001198250902234577</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0005085127195343375</v>
+        <v>0.0006356351659633219</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0002935542142949998</v>
+        <v>5.788267299067229e-05</v>
       </c>
       <c r="CB12" t="n">
-        <v>1.111376332119107e-05</v>
+        <v>0.0001691877405392006</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.0001434807054465637</v>
+        <v>0.0002453004999551922</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0001291753578698263</v>
+        <v>2.411853347439319e-05</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0002651732938829809</v>
+        <v>0.0005897206719964743</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.457556547597051e-05</v>
+        <v>5.154071186552756e-05</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0002073658251902089</v>
+        <v>0.0005108410259708762</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.4343359907798e-05</v>
+        <v>0.000111613393528387</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0001256255200132728</v>
+        <v>0.0002630231319926679</v>
       </c>
       <c r="CJ12" t="n">
-        <v>5.876259092474356e-05</v>
+        <v>6.206316174939275e-05</v>
       </c>
       <c r="CK12" t="n">
-        <v>2.232605947938282e-05</v>
+        <v>5.829035580973141e-05</v>
       </c>
       <c r="CL12" t="n">
-        <v>7.087317499099299e-05</v>
+        <v>5.174714169697836e-05</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0001368981902487576</v>
+        <v>0.0002540210552979261</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0001544863916933537</v>
+        <v>0.0002629365772008896</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.000143019889947027</v>
+        <v>0.0004089964204467833</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0002733667206484824</v>
+        <v>0.0005381263326853514</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0001859322801465169</v>
+        <v>0.0001688612828729674</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0002163054014090449</v>
+        <v>0.0001276555703952909</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.00029861691291444</v>
+        <v>3.688206561491825e-05</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0001412906276527792</v>
+        <v>0.0001852329151006415</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.17153613246046e-05</v>
+        <v>8.985903696157038e-05</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.0001064856769517064</v>
+        <v>1.237993274116889e-05</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0002013851044466719</v>
+        <v>0.0006092686089687049</v>
       </c>
       <c r="CX12" t="n">
-        <v>4.651908966479823e-05</v>
+        <v>9.093857806874439e-05</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0001995501370402053</v>
+        <v>0.0005156909464858472</v>
       </c>
       <c r="CZ12" t="n">
-        <v>7.683854346396402e-05</v>
+        <v>7.169504533521831e-05</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0001210847694892436</v>
+        <v>0.0003041156742256135</v>
       </c>
       <c r="DB12" t="n">
-        <v>7.772003300487995e-05</v>
+        <v>4.513535168371163e-05</v>
       </c>
       <c r="DC12" t="n">
-        <v>5.535559466807172e-05</v>
+        <v>1.786333086783998e-06</v>
       </c>
       <c r="DD12" t="n">
-        <v>9.398183465236798e-06</v>
+        <v>0.0001057317713275552</v>
       </c>
       <c r="DE12" t="n">
-        <v>4.413726856000721e-06</v>
+        <v>2.836321073118597e-06</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.000770165934227407</v>
+        <v>0.0009482214227318764</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.0003815925447270274</v>
+        <v>0.0005284348735585809</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.000971477827988565</v>
+        <v>0.0002454874338582158</v>
       </c>
       <c r="DI12" t="n">
-        <v>3.998012834927067e-05</v>
+        <v>3.560783807188272e-05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.284071913687512e-05</v>
+        <v>0.001031623571179807</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.0002380920777795836</v>
+        <v>0.0001340408052783459</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.0004398900782689452</v>
+        <v>0.0009886639891192317</v>
       </c>
       <c r="DM12" t="n">
-        <v>4.472472937777638e-05</v>
+        <v>0.0001439023326383904</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0003575912560336292</v>
+        <v>0.0001802623737603426</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0001802736223908141</v>
+        <v>0.0003464699839241803</v>
       </c>
       <c r="DP12" t="n">
-        <v>4.513185558607802e-05</v>
+        <v>7.198385719675571e-05</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0007256854441948235</v>
+        <v>0.0003241818048991263</v>
       </c>
       <c r="DR12" t="n">
-        <v>2.169505023630336e-06</v>
+        <v>9.06526911421679e-05</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0004614857607521117</v>
+        <v>0.0002886014990508556</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.0001122823668993078</v>
+        <v>0.0002101011050399393</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0001644136500544846</v>
+        <v>0.0003633207525126636</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0002883936394937336</v>
+        <v>0.0006500131567008793</v>
       </c>
       <c r="DW12" t="n">
-        <v>1.46808033605339e-05</v>
+        <v>7.961296796565875e-05</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0001121138629969209</v>
+        <v>0.0001679594279266894</v>
       </c>
       <c r="DY12" t="n">
-        <v>2.195279375882819e-05</v>
+        <v>7.170460594352335e-05</v>
       </c>
       <c r="DZ12" t="n">
-        <v>1.940791116794571e-05</v>
+        <v>0.0002201086608693004</v>
       </c>
       <c r="EA12" t="n">
-        <v>9.013085218612105e-05</v>
+        <v>7.628630555700511e-05</v>
       </c>
       <c r="EB12" t="n">
-        <v>6.351569027174264e-05</v>
+        <v>0.0005779325729236007</v>
       </c>
       <c r="EC12" t="n">
-        <v>8.277523011201993e-05</v>
+        <v>0.0001882143697002903</v>
       </c>
       <c r="ED12" t="n">
-        <v>3.629179991548881e-05</v>
+        <v>0.0005875323549844325</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0002742802025750279</v>
+        <v>0.0007596788345836103</v>
       </c>
       <c r="EF12" t="n">
-        <v>6.367247988237068e-05</v>
+        <v>6.890962686156854e-05</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0001612884516362101</v>
+        <v>0.000461109884781763</v>
       </c>
       <c r="EH12" t="n">
-        <v>7.910901331342757e-05</v>
+        <v>0.0002350295399082825</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.0002601831511128694</v>
+        <v>0.0004633426433429122</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0001378355518681929</v>
+        <v>0.0002012244804063812</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0002414795890217647</v>
+        <v>0.000295394886052236</v>
       </c>
       <c r="EL12" t="n">
-        <v>7.8078024671413e-05</v>
+        <v>0.0001178283855551854</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.0001359430607408285</v>
+        <v>7.853528950363398e-05</v>
       </c>
       <c r="EN12" t="n">
-        <v>2.786088953143917e-05</v>
+        <v>1.171295662061311e-05</v>
       </c>
       <c r="EO12" t="n">
-        <v>2.013976336456835e-05</v>
+        <v>6.153823051135987e-05</v>
       </c>
       <c r="EP12" t="n">
-        <v>8.380480721825734e-06</v>
+        <v>0.0003026523627340794</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0002448521263431758</v>
+        <v>5.302490899339318e-05</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0001493062591180205</v>
+        <v>0.0002519763656891882</v>
       </c>
       <c r="ES12" t="n">
-        <v>7.24681158317253e-05</v>
+        <v>0.0001943105162354186</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0007932981825433671</v>
+        <v>0.000368364475434646</v>
       </c>
       <c r="EU12" t="n">
-        <v>6.685235712211579e-05</v>
+        <v>9.361472621094435e-05</v>
       </c>
       <c r="EV12" t="n">
-        <v>5.891792898182757e-05</v>
+        <v>0.0002703289210330695</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.0001961019006557763</v>
+        <v>0.0003810776688624173</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.0001629014150239527</v>
+        <v>2.731896529439837e-06</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0002267359086545184</v>
+        <v>0.0006677188212051988</v>
       </c>
       <c r="EZ12" t="n">
-        <v>1.433560191799188e-05</v>
+        <v>5.226376379141584e-05</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.000205799748073332</v>
+        <v>0.0005601415177807212</v>
       </c>
       <c r="FB12" t="n">
-        <v>2.189858423662372e-05</v>
+        <v>9.843154111877084e-05</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0001436485472368076</v>
+        <v>0.0002923568827100098</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0001219085534103215</v>
+        <v>5.414860061137006e-05</v>
       </c>
       <c r="FE12" t="n">
-        <v>2.9000253562117e-05</v>
+        <v>0.000142188451718539</v>
       </c>
       <c r="FF12" t="n">
-        <v>5.373399744712515e-06</v>
+        <v>0.0001625672593945637</v>
       </c>
       <c r="FG12" t="n">
-        <v>7.603953417856246e-05</v>
+        <v>0.0001162856424343772</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0003377290850039572</v>
+        <v>0.0003017142880707979</v>
       </c>
       <c r="FI12" t="n">
-        <v>8.517147216480225e-05</v>
+        <v>0.0001482064981246367</v>
       </c>
       <c r="FJ12" t="n">
-        <v>7.484798697987571e-05</v>
+        <v>0.0001609087339602411</v>
       </c>
       <c r="FK12" t="n">
-        <v>4.977643766324036e-05</v>
+        <v>0.0001213264331454411</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0001587465812917799</v>
+        <v>0.0001842405908973888</v>
       </c>
       <c r="FM12" t="n">
-        <v>9.209741983795539e-05</v>
+        <v>8.668863301863894e-05</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.0001041073119267821</v>
+        <v>9.903611498884857e-05</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.0003015320980921388</v>
+        <v>0.0001240682904608548</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0003406261093914509</v>
+        <v>0.0004286058538127691</v>
       </c>
       <c r="FQ12" t="n">
-        <v>4.119679215364158e-05</v>
+        <v>0.0004462437937036157</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.0005694996798411012</v>
+        <v>0.0004042382934130728</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0001024410230456851</v>
+        <v>0.0006327718147076666</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0006959004676900804</v>
+        <v>7.343085599131882e-05</v>
       </c>
       <c r="FU12" t="n">
-        <v>1.347967918263748e-05</v>
+        <v>0.0001943185488926247</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.0003309909370727837</v>
+        <v>0.0001503945095464587</v>
       </c>
       <c r="FW12" t="n">
-        <v>3.487047797534615e-05</v>
+        <v>0.0004323849861975759</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.0001026796599035151</v>
+        <v>0.0005213686963543296</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0001149109884863719</v>
+        <v>0.0004558542277663946</v>
       </c>
       <c r="FZ12" t="n">
-        <v>6.498173752333969e-05</v>
+        <v>0.0003371396451257169</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.000130480868392624</v>
+        <v>3.772538184421137e-05</v>
       </c>
       <c r="GB12" t="n">
-        <v>6.477900024037808e-05</v>
+        <v>0.000358275487087667</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.0004471438005566597</v>
+        <v>0.0001308305072598159</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.000315663666697219</v>
+        <v>0.0004770686791744083</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0004667126922868192</v>
+        <v>0.0003875271650031209</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.000271512137260288</v>
+        <v>0.0003198385238647461</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.0002893017081078142</v>
+        <v>0.0001880280033219606</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.003637761110439897</v>
+        <v>0.03481386601924896</v>
       </c>
       <c r="B13" t="n">
-        <v>0.009370582178235054</v>
+        <v>0.08185215294361115</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002712933113798499</v>
+        <v>0.003956247121095657</v>
       </c>
       <c r="D13" t="n">
-        <v>0.006992776412516832</v>
+        <v>0.02874638885259628</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002021302236244082</v>
+        <v>0.00863068550825119</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0009575951262377203</v>
+        <v>0.1157702580094337</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002252847421914339</v>
+        <v>0.001069065881893039</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001562823774293065</v>
+        <v>0.0624389536678791</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0002366331464145333</v>
+        <v>0.01260269433259964</v>
       </c>
       <c r="J13" t="n">
-        <v>0.004861998837441206</v>
+        <v>0.03907568380236626</v>
       </c>
       <c r="K13" t="n">
-        <v>0.008110152557492256</v>
+        <v>0.1073542609810829</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001636975677683949</v>
+        <v>0.02597680874168873</v>
       </c>
       <c r="M13" t="n">
-        <v>0.005110045429319143</v>
+        <v>0.04482852667570114</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0008722128113731742</v>
+        <v>0.05771904438734055</v>
       </c>
       <c r="O13" t="n">
-        <v>0.00222791638225317</v>
+        <v>0.1237671375274658</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001105625415220857</v>
+        <v>0.0003707387950271368</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.003460514126345515</v>
+        <v>0.04850194230675697</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0006537887966260314</v>
+        <v>0.03094398230314255</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001075427164323628</v>
+        <v>0.006450137123465538</v>
       </c>
       <c r="T13" t="n">
-        <v>0.001717674895189703</v>
+        <v>0.01401644293218851</v>
       </c>
       <c r="U13" t="n">
-        <v>0.000505558040458709</v>
+        <v>0.02127837017178535</v>
       </c>
       <c r="V13" t="n">
-        <v>0.001573743647895753</v>
+        <v>0.01385458000004292</v>
       </c>
       <c r="W13" t="n">
-        <v>0.001057093963027</v>
+        <v>0.006910591386258602</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0003562960773706436</v>
+        <v>0.0330180786550045</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.001136172679252923</v>
+        <v>0.01394302025437355</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0002544808376114815</v>
+        <v>0.02252285927534103</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.001254830160178244</v>
+        <v>0.007646087557077408</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0002662557526491582</v>
+        <v>0.01883622445166111</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.002307188231498003</v>
+        <v>0.01163776218891144</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0003613789158407599</v>
+        <v>0.0003313877969048917</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0003333644126541913</v>
+        <v>0.0007083253003656864</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0003127947566099465</v>
+        <v>0.04069309309124947</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.001074599684216082</v>
+        <v>0.01271680183708668</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.001481088576838374</v>
+        <v>0.02360484749078751</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0005662526236847043</v>
+        <v>0.02779253385961056</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0006978820310905576</v>
+        <v>0.003535511204972863</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0004471091669984162</v>
+        <v>0.00776458065956831</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.001073380466550589</v>
+        <v>0.02159369736909866</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0002820712979882956</v>
+        <v>0.005593751091510057</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0009332777699455619</v>
+        <v>0.02902979962527752</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0006057146238163114</v>
+        <v>0.004868359304964542</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0006717246142216027</v>
+        <v>0.0128187071532011</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.09450463950634e-05</v>
+        <v>0.003043659497052431</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0002558222913648933</v>
+        <v>0.02234470658004284</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0006238581845536828</v>
+        <v>0.01610188558697701</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.001347802812233567</v>
+        <v>0.02187736704945564</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0039629559032619</v>
+        <v>0.1441469192504883</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.001615933608263731</v>
+        <v>0.005469175055623055</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.001958383247256279</v>
+        <v>0.01291692908853292</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.001146082300692797</v>
+        <v>0.02290881797671318</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.00107498187571764</v>
+        <v>0.08201668411493301</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0001831768313422799</v>
+        <v>0.001983821857720613</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0009092308464460075</v>
+        <v>0.009668616577982903</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.001502083265222609</v>
+        <v>0.01358955912292004</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.003996412269771099</v>
+        <v>0.03493936359882355</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.002463390585035086</v>
+        <v>0.03375793993473053</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.001627207617275417</v>
+        <v>0.003957050852477551</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.001071306993253529</v>
+        <v>0.006759717129170895</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.003458452876657248</v>
+        <v>0.001602661563083529</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.54012188129127e-05</v>
+        <v>0.01033949665725231</v>
       </c>
       <c r="BI13" t="n">
-        <v>8.333751611644402e-05</v>
+        <v>0.02116443775594234</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.004779931157827377</v>
+        <v>0.02470949105918407</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0001522533420938998</v>
+        <v>0.005726221948862076</v>
       </c>
       <c r="BL13" t="n">
-        <v>5.960202543064952e-05</v>
+        <v>0.01172524131834507</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.001256404211744666</v>
+        <v>0.01970715261995792</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0003936212160624564</v>
+        <v>0.01130477525293827</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.001567097846418619</v>
+        <v>0.0005149627104401588</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0007540893857367337</v>
+        <v>0.02471297234296799</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0004291333607397974</v>
+        <v>0.02677101641893387</v>
       </c>
       <c r="BR13" t="n">
-        <v>3.170251147821546e-06</v>
+        <v>0.007492753677070141</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.94650734658353e-05</v>
+        <v>0.006820458918809891</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0004124552360735834</v>
+        <v>0.01955381780862808</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.001465937471948564</v>
+        <v>0.0003102803602814674</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.001853113179095089</v>
+        <v>0.06008302420377731</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.001895142020657659</v>
+        <v>0.003366339020431042</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.001668121665716171</v>
+        <v>0.03096348792314529</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0002288428513566032</v>
+        <v>0.002818957436829805</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0001531832385808229</v>
+        <v>0.04780960455536842</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.001119241467677057</v>
+        <v>0.01413963735103607</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.00125212105922401</v>
+        <v>0.01980878971517086</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.002170397667214274</v>
+        <v>0.00410107197239995</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0007842627237550914</v>
+        <v>0.01285807974636555</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.001593487919308245</v>
+        <v>0.02901510149240494</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0005228095105849206</v>
+        <v>0.003565154504030943</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0008114443626254797</v>
+        <v>0.01287581771612167</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0005937068490311503</v>
+        <v>0.01106398459523916</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.521570058888756e-05</v>
+        <v>0.02452022209763527</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0001728642382659018</v>
+        <v>0.003708230331540108</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0001880371564766392</v>
+        <v>0.007060695439577103</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.001300011994317174</v>
+        <v>0.0005529418122023344</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0005726416129618883</v>
+        <v>0.03775368258357048</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0007128420402295887</v>
+        <v>0.03197093680500984</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0002937648387160152</v>
+        <v>0.006291614845395088</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.001542267389595509</v>
+        <v>0.01016639638692141</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.000589338771533221</v>
+        <v>0.005530867725610733</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0006280631059780717</v>
+        <v>0.002990449778735638</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.002028240589424968</v>
+        <v>0.0097954161465168</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.001668871147558093</v>
+        <v>0.01382602099329233</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0003019589348696172</v>
+        <v>0.009339801035821438</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0007325385231524706</v>
+        <v>0.005164803005754948</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.001392842154018581</v>
+        <v>0.02073496952652931</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0008477261872030795</v>
+        <v>0.009536337107419968</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0013158586807549</v>
+        <v>0.01764246448874474</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0006149160908535123</v>
+        <v>0.01317662093788385</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0001513566530775279</v>
+        <v>0.03132493048906326</v>
       </c>
       <c r="DB13" t="n">
-        <v>8.653292752569541e-05</v>
+        <v>0.0006796835223212838</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0001139016894740053</v>
+        <v>0.002540392801165581</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.001180918421596289</v>
+        <v>0.002197740832343698</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0005505774170160294</v>
+        <v>0.004469754174351692</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.003539283061400056</v>
+        <v>0.03288449347019196</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.001040932373143733</v>
+        <v>0.002467793878167868</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.004443579819053411</v>
+        <v>0.001879449933767319</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0005328202387318015</v>
+        <v>0.002908005844801664</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.001352062681689858</v>
+        <v>0.03024430572986603</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.003197374287992716</v>
+        <v>0.01794526539742947</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.002423298545181751</v>
+        <v>0.05244923010468483</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0003443943278398365</v>
+        <v>0.004592698067426682</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0006473750690929592</v>
+        <v>0.0005687633529305458</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0002769241400528699</v>
+        <v>0.009697689674794674</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0005050295731052756</v>
+        <v>0.004198196344077587</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0002147078484995291</v>
+        <v>0.0005618579452857375</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0009536162251606584</v>
+        <v>0.0002359147183597088</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0002535475650802255</v>
+        <v>0.02420524694025517</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0008927025482989848</v>
+        <v>0.006886905990540981</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.00037793317460455</v>
+        <v>0.01737913861870766</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0006328641902655363</v>
+        <v>0.000220505753532052</v>
       </c>
       <c r="DW13" t="n">
-        <v>4.088261630386114e-05</v>
+        <v>0.02127325907349586</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0004501552903093398</v>
+        <v>0.02679647691547871</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.001472890260629356</v>
+        <v>0.02377244271337986</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0008050636388361454</v>
+        <v>0.005192267708480358</v>
       </c>
       <c r="EA13" t="n">
-        <v>4.037785402033478e-06</v>
+        <v>0.02710439637303352</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0006646105321124196</v>
+        <v>0.02613142877817154</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0003073582192882895</v>
+        <v>0.007231650408357382</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0009372593485750258</v>
+        <v>0.0292494148015976</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0007340176380239427</v>
+        <v>0.0232730396091938</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0002161002339562401</v>
+        <v>0.01875872723758221</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.001646044314838946</v>
+        <v>0.0104845417663455</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0002679052413441241</v>
+        <v>0.002542614936828613</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0009103810298256576</v>
+        <v>0.004375225398689508</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0002884630230255425</v>
+        <v>0.0153489513322711</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0002544250746723264</v>
+        <v>0.01185713615268469</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0002190591767430305</v>
+        <v>0.001277956878766418</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0004980251542292535</v>
+        <v>0.01179818715900183</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.001696521765552461</v>
+        <v>0.004315514117479324</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0005102815921418369</v>
+        <v>0.001424722373485565</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.001449955278076231</v>
+        <v>0.01193561311811209</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0007121245143935084</v>
+        <v>0.006896523758769035</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0005455994978547096</v>
+        <v>0.03537651896476746</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0002938881516456604</v>
+        <v>0.01717614568769932</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0002031426411122084</v>
+        <v>0.008886718191206455</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0006895513506606221</v>
+        <v>0.007482858374714851</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.000215680236578919</v>
+        <v>0.004185053985565901</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0005146603216417134</v>
+        <v>0.01466839667409658</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0004514154279604554</v>
+        <v>0.01314288750290871</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.001564140780828893</v>
+        <v>0.02921349368989468</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0005784640088677406</v>
+        <v>0.003443290945142508</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.001156442565843463</v>
+        <v>0.01330168545246124</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0004928705166094005</v>
+        <v>0.00188935361802578</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0001989565207622945</v>
+        <v>0.02875876612961292</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0001258003176189959</v>
+        <v>0.004414351657032967</v>
       </c>
       <c r="FE13" t="n">
-        <v>9.238874918082729e-05</v>
+        <v>0.005628078244626522</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.001618185546249151</v>
+        <v>0.003263026941567659</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0002769686398096383</v>
+        <v>0.006339611019939184</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0002153332170564681</v>
+        <v>0.01903979480266571</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0006626716931350529</v>
+        <v>0.009441381320357323</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.001655433443374932</v>
+        <v>0.009346588514745235</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0001015994785120711</v>
+        <v>0.005853157490491867</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.001045346725732088</v>
+        <v>0.02611307054758072</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0001014992158161476</v>
+        <v>0.01094287168234587</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0005008933367207646</v>
+        <v>0.01063646096736193</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.001168946851976216</v>
+        <v>0.02563256025314331</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0004003139911219478</v>
+        <v>0.01299822237342596</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0006873662932775915</v>
+        <v>0.003735113888978958</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.002660768572241068</v>
+        <v>0.01016383431851864</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.001718963147141039</v>
+        <v>0.01369033101946115</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0006335775251500309</v>
+        <v>0.0215121153742075</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0002579376450739801</v>
+        <v>0.007545780390501022</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.000247559801209718</v>
+        <v>0.0410490594804287</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0007533543976023793</v>
+        <v>0.0606086440384388</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.001351053942926228</v>
+        <v>0.005350914318114519</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.001310058520175517</v>
+        <v>0.02937131375074387</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0006568435346707702</v>
+        <v>0.005306477658450603</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0002742279903031886</v>
+        <v>0.03021461889147758</v>
       </c>
       <c r="GB13" t="n">
-        <v>9.296754433307797e-05</v>
+        <v>0.0002390607260167599</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0005941151175647974</v>
+        <v>0.04455824941396713</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.001414127531461418</v>
+        <v>0.02483919262886047</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.00367822777479887</v>
+        <v>4.509603604674339e-05</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0003636680776253343</v>
+        <v>0.01154911797493696</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0002918258542194963</v>
+        <v>0.002944580279290676</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0001394295977661386</v>
+        <v>7.474656626982323e-08</v>
       </c>
       <c r="B14" t="n">
-        <v>1.80472488864325e-05</v>
+        <v>2.506862529116916e-06</v>
       </c>
       <c r="C14" t="n">
-        <v>1.461202373320702e-05</v>
+        <v>7.4411013883946e-07</v>
       </c>
       <c r="D14" t="n">
-        <v>3.115511208306998e-05</v>
+        <v>1.639677861930977e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0001105163973988965</v>
+        <v>1.490160343564639e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>1.811741458368488e-05</v>
+        <v>3.153835677949246e-06</v>
       </c>
       <c r="G14" t="n">
-        <v>3.335367364343256e-05</v>
+        <v>5.530918656404538e-07</v>
       </c>
       <c r="H14" t="n">
-        <v>1.819655699364375e-05</v>
+        <v>9.599522172720754e-07</v>
       </c>
       <c r="I14" t="n">
-        <v>5.535543550649891e-06</v>
+        <v>3.934212315925834e-07</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001319081202382222</v>
+        <v>2.656664719324908e-07</v>
       </c>
       <c r="K14" t="n">
-        <v>1.188560645459802e-06</v>
+        <v>2.166161721106619e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>3.736022699740715e-05</v>
+        <v>1.355054337182082e-06</v>
       </c>
       <c r="M14" t="n">
-        <v>5.868650077900384e-06</v>
+        <v>2.321150532225147e-06</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0001013706933008507</v>
+        <v>1.403881100259241e-08</v>
       </c>
       <c r="O14" t="n">
-        <v>5.397948370955419e-06</v>
+        <v>3.449278437983594e-06</v>
       </c>
       <c r="P14" t="n">
-        <v>3.982935231761076e-05</v>
+        <v>4.083228191120725e-07</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.390840679960093e-05</v>
+        <v>3.416824370106042e-07</v>
       </c>
       <c r="R14" t="n">
-        <v>1.811579022614751e-05</v>
+        <v>5.517393333320797e-07</v>
       </c>
       <c r="S14" t="n">
-        <v>2.771802428469528e-06</v>
+        <v>4.880972710452625e-07</v>
       </c>
       <c r="T14" t="n">
-        <v>2.644033520482481e-05</v>
+        <v>3.842760634142905e-07</v>
       </c>
       <c r="U14" t="n">
-        <v>5.347379101294791e-06</v>
+        <v>5.728583118980168e-07</v>
       </c>
       <c r="V14" t="n">
-        <v>2.132415102096274e-05</v>
+        <v>1.009838257459705e-07</v>
       </c>
       <c r="W14" t="n">
-        <v>8.33458670967957e-06</v>
+        <v>1.486180565279938e-07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.084928589989431e-05</v>
+        <v>6.040454536559992e-07</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.362512532272376e-05</v>
+        <v>1.740622366241951e-07</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.123275044141337e-05</v>
+        <v>7.794022849338944e-08</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.77498621068662e-06</v>
+        <v>5.863308416564905e-08</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.442159166093916e-05</v>
+        <v>1.796850312985043e-07</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.537127329560462e-05</v>
+        <v>9.898457165036234e-08</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.174903536593774e-05</v>
+        <v>3.877596270740469e-07</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.934523061208893e-05</v>
+        <v>2.540824084462656e-08</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.14092342503136e-05</v>
+        <v>1.637470603554902e-07</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.592469172668643e-08</v>
+        <v>8.546501248929417e-07</v>
       </c>
       <c r="AH14" t="n">
-        <v>7.404560165014118e-06</v>
+        <v>3.651576321317407e-07</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.545019196986686e-05</v>
+        <v>2.652021180438169e-07</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.764724038366694e-05</v>
+        <v>4.291559037028492e-07</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.944286072510295e-05</v>
+        <v>9.67000630680559e-08</v>
       </c>
       <c r="AL14" t="n">
-        <v>9.492993740423117e-06</v>
+        <v>1.221283980612498e-07</v>
       </c>
       <c r="AM14" t="n">
-        <v>8.395653821935412e-06</v>
+        <v>4.971153089172731e-07</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.448634222673718e-05</v>
+        <v>1.244002760358853e-06</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.994526974158362e-05</v>
+        <v>5.087219960842049e-07</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.725194008235121e-06</v>
+        <v>5.570372536567447e-07</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.452098543581087e-06</v>
+        <v>2.969646004657989e-07</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.088697121711448e-05</v>
+        <v>2.515611470244039e-07</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.558327418635599e-06</v>
+        <v>8.263253192808406e-08</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.903056343318895e-05</v>
+        <v>1.746691822290813e-07</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.524826181295794e-06</v>
+        <v>1.375332203679136e-06</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.43562838275102e-05</v>
+        <v>8.97885740869242e-07</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.216736513422802e-05</v>
+        <v>1.136100763687864e-06</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0001119832886615768</v>
+        <v>8.998767953016795e-07</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.681010508036707e-05</v>
+        <v>1.693108288236544e-06</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.065239292889601e-06</v>
+        <v>8.819534969006781e-08</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.754403173341416e-05</v>
+        <v>3.149349225850528e-09</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.087617758661509e-07</v>
+        <v>3.176534733029257e-07</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.087110962951556e-05</v>
+        <v>2.836290775576344e-07</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.447606625035405e-05</v>
+        <v>5.236191213953134e-07</v>
       </c>
       <c r="BE14" t="n">
-        <v>3.152597855660133e-05</v>
+        <v>6.302849442363367e-08</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.318434169661487e-05</v>
+        <v>1.203124213589035e-07</v>
       </c>
       <c r="BG14" t="n">
-        <v>9.722040886117611e-06</v>
+        <v>9.290152434004995e-07</v>
       </c>
       <c r="BH14" t="n">
-        <v>1.836715455283411e-05</v>
+        <v>3.248809719025303e-07</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.329170456505381e-05</v>
+        <v>2.555304376983258e-07</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1.78054760908708e-05</v>
+        <v>4.997986593480164e-07</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.886161226138938e-05</v>
+        <v>4.422263941705751e-07</v>
       </c>
       <c r="BL14" t="n">
-        <v>8.699477803020272e-06</v>
+        <v>4.990096158508095e-07</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.554131813463755e-05</v>
+        <v>6.242746053430892e-08</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.180712024506647e-05</v>
+        <v>5.941705012446619e-07</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.497891025792342e-05</v>
+        <v>4.730890452719905e-07</v>
       </c>
       <c r="BP14" t="n">
-        <v>1.885851452243514e-05</v>
+        <v>4.71840820637226e-07</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.734504950145492e-06</v>
+        <v>3.110359045876976e-07</v>
       </c>
       <c r="BR14" t="n">
-        <v>3.154212890876806e-06</v>
+        <v>2.308711373188999e-07</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.359366797260009e-05</v>
+        <v>1.282342623198929e-07</v>
       </c>
       <c r="BT14" t="n">
-        <v>1.497624089097371e-05</v>
+        <v>4.404276126024342e-07</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.87747677450534e-05</v>
+        <v>3.943516446724971e-07</v>
       </c>
       <c r="BV14" t="n">
-        <v>2.21100299313548e-06</v>
+        <v>8.749482276471099e-07</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.616758921358269e-07</v>
+        <v>9.381216159454198e-08</v>
       </c>
       <c r="BX14" t="n">
-        <v>1.853126195783261e-05</v>
+        <v>8.283547003884451e-07</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.004407987347804e-05</v>
+        <v>4.380160234518371e-08</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.151362903328845e-05</v>
+        <v>1.05985577647516e-06</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.874062945717014e-05</v>
+        <v>3.655247837741626e-08</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.986569208791479e-05</v>
+        <v>4.67996628117362e-08</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.157173937826883e-05</v>
+        <v>1.04788471233519e-08</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.359355494263582e-05</v>
+        <v>2.232185636330541e-08</v>
       </c>
       <c r="CE14" t="n">
-        <v>2.210062120866496e-05</v>
+        <v>8.020679160836153e-07</v>
       </c>
       <c r="CF14" t="n">
-        <v>6.63496848574141e-07</v>
+        <v>2.241664134317034e-07</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.484690296318149e-06</v>
+        <v>6.451812737395812e-07</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.835225884860847e-05</v>
+        <v>1.363421660016684e-07</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.005645060558891e-07</v>
+        <v>5.731595251745603e-07</v>
       </c>
       <c r="CJ14" t="n">
-        <v>7.416235348500777e-06</v>
+        <v>1.745779698580918e-08</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.461399187974166e-05</v>
+        <v>2.821234090788494e-07</v>
       </c>
       <c r="CL14" t="n">
-        <v>6.269365712796571e-06</v>
+        <v>5.899187982549847e-08</v>
       </c>
       <c r="CM14" t="n">
-        <v>3.940103852073662e-06</v>
+        <v>6.769433298359218e-07</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.521732610854087e-05</v>
+        <v>2.406870294180408e-07</v>
       </c>
       <c r="CO14" t="n">
-        <v>3.811307806245168e-06</v>
+        <v>5.296878953231499e-07</v>
       </c>
       <c r="CP14" t="n">
-        <v>4.765485300595174e-06</v>
+        <v>8.346429467565031e-07</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.126962317561265e-05</v>
+        <v>1.084119617189572e-06</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.146705562860006e-05</v>
+        <v>3.922620805951738e-07</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.524772935430519e-05</v>
+        <v>2.691086251616071e-07</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.704221671796404e-05</v>
+        <v>3.787251898756949e-07</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.645486554480158e-05</v>
+        <v>1.950145076534682e-07</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.964743205462582e-05</v>
+        <v>1.203446231556882e-07</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.931834776769392e-05</v>
+        <v>6.648846238022088e-07</v>
       </c>
       <c r="CX14" t="n">
-        <v>2.377872078795917e-06</v>
+        <v>3.459478250533721e-07</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.546470684843371e-07</v>
+        <v>6.583038043572742e-07</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.187484278692864e-05</v>
+        <v>1.014176760349983e-07</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.512610538156878e-06</v>
+        <v>5.513791165867588e-07</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.33814501168672e-05</v>
+        <v>4.604817149811424e-08</v>
       </c>
       <c r="DC14" t="n">
-        <v>9.09486880118493e-06</v>
+        <v>2.830112748597458e-07</v>
       </c>
       <c r="DD14" t="n">
-        <v>7.785363777657039e-06</v>
+        <v>3.526593772562592e-08</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.996828905248549e-05</v>
+        <v>4.942978648614371e-07</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.982175126613583e-05</v>
+        <v>8.907205142349994e-07</v>
       </c>
       <c r="DG14" t="n">
-        <v>5.002339457860216e-05</v>
+        <v>7.049551413729205e-07</v>
       </c>
       <c r="DH14" t="n">
-        <v>3.043762990273535e-05</v>
+        <v>6.6707059431792e-08</v>
       </c>
       <c r="DI14" t="n">
-        <v>1.776087628968526e-05</v>
+        <v>4.437761162989773e-07</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.250771674676798e-05</v>
+        <v>8.782463396528328e-07</v>
       </c>
       <c r="DK14" t="n">
-        <v>8.417545359407086e-06</v>
+        <v>3.240641319735005e-07</v>
       </c>
       <c r="DL14" t="n">
-        <v>6.826950993854553e-05</v>
+        <v>1.400221776748367e-06</v>
       </c>
       <c r="DM14" t="n">
-        <v>5.162834895600099e-06</v>
+        <v>2.148995292827749e-07</v>
       </c>
       <c r="DN14" t="n">
-        <v>8.112835530482698e-06</v>
+        <v>1.145398371704687e-07</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.508222521806601e-05</v>
+        <v>5.315349937973224e-08</v>
       </c>
       <c r="DP14" t="n">
-        <v>4.658319085137919e-06</v>
+        <v>2.212431553516581e-07</v>
       </c>
       <c r="DQ14" t="n">
-        <v>2.644202368173865e-06</v>
+        <v>5.890669285690819e-08</v>
       </c>
       <c r="DR14" t="n">
-        <v>2.529833182052244e-05</v>
+        <v>1.776595581759466e-07</v>
       </c>
       <c r="DS14" t="n">
-        <v>4.811363396584056e-07</v>
+        <v>2.749003158442065e-07</v>
       </c>
       <c r="DT14" t="n">
-        <v>5.452092409541365e-06</v>
+        <v>1.283163726384373e-07</v>
       </c>
       <c r="DU14" t="n">
-        <v>3.290401946287602e-05</v>
+        <v>2.238379721575257e-07</v>
       </c>
       <c r="DV14" t="n">
-        <v>8.015103048819583e-06</v>
+        <v>3.630423179856734e-07</v>
       </c>
       <c r="DW14" t="n">
-        <v>1.46149886859348e-06</v>
+        <v>5.793398472064837e-08</v>
       </c>
       <c r="DX14" t="n">
-        <v>3.337869929964654e-05</v>
+        <v>5.80509265546425e-07</v>
       </c>
       <c r="DY14" t="n">
-        <v>3.26235067404923e-07</v>
+        <v>1.489263922849204e-06</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.846047209459357e-06</v>
+        <v>1.446523896220242e-07</v>
       </c>
       <c r="EA14" t="n">
-        <v>2.717746247071773e-05</v>
+        <v>3.385500946251341e-08</v>
       </c>
       <c r="EB14" t="n">
-        <v>3.884681973431725e-06</v>
+        <v>1.447955710887072e-08</v>
       </c>
       <c r="EC14" t="n">
-        <v>6.182333891047165e-06</v>
+        <v>6.081484826836459e-08</v>
       </c>
       <c r="ED14" t="n">
-        <v>1.239128505403642e-05</v>
+        <v>1.108521132664464e-06</v>
       </c>
       <c r="EE14" t="n">
-        <v>3.306640792288817e-06</v>
+        <v>9.088258252631931e-07</v>
       </c>
       <c r="EF14" t="n">
-        <v>2.375889744143933e-05</v>
+        <v>4.240263251631404e-07</v>
       </c>
       <c r="EG14" t="n">
-        <v>3.072299296036363e-05</v>
+        <v>8.604765753261745e-07</v>
       </c>
       <c r="EH14" t="n">
-        <v>6.000251232762821e-06</v>
+        <v>6.991143663981347e-09</v>
       </c>
       <c r="EI14" t="n">
-        <v>1.699482709227595e-05</v>
+        <v>2.11137660244276e-07</v>
       </c>
       <c r="EJ14" t="n">
-        <v>2.610369483591057e-05</v>
+        <v>1.874653037248208e-07</v>
       </c>
       <c r="EK14" t="n">
-        <v>7.499455477955053e-06</v>
+        <v>5.671811891261314e-07</v>
       </c>
       <c r="EL14" t="n">
-        <v>3.766583631659159e-07</v>
+        <v>5.44226423926375e-08</v>
       </c>
       <c r="EM14" t="n">
-        <v>1.729801965666411e-06</v>
+        <v>2.422559930437274e-07</v>
       </c>
       <c r="EN14" t="n">
-        <v>1.036947651300579e-06</v>
+        <v>3.541357784797583e-07</v>
       </c>
       <c r="EO14" t="n">
-        <v>1.213266932609258e-05</v>
+        <v>3.09480014948349e-07</v>
       </c>
       <c r="EP14" t="n">
-        <v>7.689238373131957e-06</v>
+        <v>1.237885726368404e-06</v>
       </c>
       <c r="EQ14" t="n">
-        <v>5.346041234588483e-06</v>
+        <v>5.343078157693526e-08</v>
       </c>
       <c r="ER14" t="n">
-        <v>9.061953278433066e-06</v>
+        <v>1.091321337298723e-06</v>
       </c>
       <c r="ES14" t="n">
-        <v>2.40792960539693e-05</v>
+        <v>1.492917078849132e-07</v>
       </c>
       <c r="ET14" t="n">
-        <v>9.129617865255568e-06</v>
+        <v>7.39444772079878e-07</v>
       </c>
       <c r="EU14" t="n">
-        <v>3.120930341538042e-05</v>
+        <v>5.284054509502312e-07</v>
       </c>
       <c r="EV14" t="n">
-        <v>5.895181402593153e-06</v>
+        <v>1.110290881456422e-07</v>
       </c>
       <c r="EW14" t="n">
-        <v>4.706954769062577e-06</v>
+        <v>5.302159138409479e-07</v>
       </c>
       <c r="EX14" t="n">
-        <v>1.845167753344867e-05</v>
+        <v>1.033280199180808e-07</v>
       </c>
       <c r="EY14" t="n">
-        <v>1.829385109886061e-05</v>
+        <v>9.316370892520354e-07</v>
       </c>
       <c r="EZ14" t="n">
-        <v>6.221441253728699e-06</v>
+        <v>1.928913206938887e-07</v>
       </c>
       <c r="FA14" t="n">
-        <v>2.808495992212556e-06</v>
+        <v>6.734775297445594e-07</v>
       </c>
       <c r="FB14" t="n">
-        <v>1.951011836354155e-05</v>
+        <v>2.142831618812124e-07</v>
       </c>
       <c r="FC14" t="n">
-        <v>7.051149850667571e-07</v>
+        <v>6.434793249354698e-07</v>
       </c>
       <c r="FD14" t="n">
-        <v>5.722258720197715e-06</v>
+        <v>3.203917131600065e-10</v>
       </c>
       <c r="FE14" t="n">
-        <v>1.532813075755257e-05</v>
+        <v>2.500712810160621e-07</v>
       </c>
       <c r="FF14" t="n">
-        <v>4.531390004558489e-06</v>
+        <v>8.291670638982396e-08</v>
       </c>
       <c r="FG14" t="n">
-        <v>1.490684098826023e-05</v>
+        <v>2.63083990148516e-08</v>
       </c>
       <c r="FH14" t="n">
-        <v>3.61195307050366e-05</v>
+        <v>5.912748406444734e-07</v>
       </c>
       <c r="FI14" t="n">
-        <v>8.049390999076422e-06</v>
+        <v>1.04497371467005e-06</v>
       </c>
       <c r="FJ14" t="n">
-        <v>5.447364401334198e-06</v>
+        <v>2.274765336096607e-07</v>
       </c>
       <c r="FK14" t="n">
-        <v>2.432184192002751e-05</v>
+        <v>3.573227331798989e-07</v>
       </c>
       <c r="FL14" t="n">
-        <v>3.914669832738582e-06</v>
+        <v>1.740052766763256e-06</v>
       </c>
       <c r="FM14" t="n">
-        <v>4.141916633670917e-06</v>
+        <v>2.106755374597924e-07</v>
       </c>
       <c r="FN14" t="n">
-        <v>8.983297448139638e-06</v>
+        <v>4.690626838055323e-07</v>
       </c>
       <c r="FO14" t="n">
-        <v>5.638509719574358e-06</v>
+        <v>6.971351353968203e-07</v>
       </c>
       <c r="FP14" t="n">
-        <v>2.766890065686312e-05</v>
+        <v>8.896982990336255e-07</v>
       </c>
       <c r="FQ14" t="n">
-        <v>3.168777038808912e-05</v>
+        <v>4.420847403707739e-07</v>
       </c>
       <c r="FR14" t="n">
-        <v>3.829683555522934e-05</v>
+        <v>1.698803202998533e-06</v>
       </c>
       <c r="FS14" t="n">
-        <v>2.055145523627289e-05</v>
+        <v>1.675841758697061e-07</v>
       </c>
       <c r="FT14" t="n">
-        <v>7.063178782118484e-05</v>
+        <v>3.3286517009401e-07</v>
       </c>
       <c r="FU14" t="n">
-        <v>1.336961940978654e-05</v>
+        <v>2.373302407931988e-07</v>
       </c>
       <c r="FV14" t="n">
-        <v>2.277795647387393e-05</v>
+        <v>3.222735358576756e-07</v>
       </c>
       <c r="FW14" t="n">
-        <v>1.604051431058906e-05</v>
+        <v>7.479134751520178e-07</v>
       </c>
       <c r="FX14" t="n">
-        <v>1.150210027844878e-05</v>
+        <v>3.300994819710468e-07</v>
       </c>
       <c r="FY14" t="n">
-        <v>9.288889486924745e-06</v>
+        <v>3.312666478905157e-07</v>
       </c>
       <c r="FZ14" t="n">
-        <v>9.01883868209552e-06</v>
+        <v>3.38928174414832e-08</v>
       </c>
       <c r="GA14" t="n">
-        <v>8.616207196610048e-06</v>
+        <v>1.158952045443584e-06</v>
       </c>
       <c r="GB14" t="n">
-        <v>2.264671275042929e-05</v>
+        <v>9.532578815196757e-07</v>
       </c>
       <c r="GC14" t="n">
-        <v>3.117313826805912e-05</v>
+        <v>1.090534283321176e-06</v>
       </c>
       <c r="GD14" t="n">
-        <v>2.942370338132605e-05</v>
+        <v>9.139109238276433e-07</v>
       </c>
       <c r="GE14" t="n">
-        <v>2.847768519131932e-05</v>
+        <v>3.411938394037861e-07</v>
       </c>
       <c r="GF14" t="n">
-        <v>1.638433423067909e-05</v>
+        <v>1.097025403851148e-07</v>
       </c>
       <c r="GG14" t="n">
-        <v>6.129763278295286e-06</v>
+        <v>5.328791985448333e-08</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.002463779877871275</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.001929244492202997</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.001206955523230135</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.007178302388638258</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.006679259240627289</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0008862251415848732</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.002281703054904938</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.001436106394976377</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.00326817505992949</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.001298959832638502</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.00267742807045579</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.00143548334017396</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.009375733323395252</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.005292300134897232</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.002659517107531428</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.00182852172292769</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.004965537693351507</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.003015717025846243</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8.617830462753773e-05</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.00162865687161684</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.0006313546909950674</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.0005452060140669346</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.001254598260857165</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.001696678926236928</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.001417613122612238</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.0003619501658249646</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.894527955912054e-05</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.001867636688984931</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.0004904487868770957</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.0009059957810677588</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.0009869949426501989</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.003787653520703316</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.001280951662920415</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>6.107147783041e-07</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.0002753128355834633</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.002139371586963534</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.0002992754452861845</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.0005100163398310542</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.0006689447327516973</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.001446421723812819</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.00388109078630805</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.002247413620352745</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.002268372569233179</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.002281258814036846</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.0005883238627575338</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.001037336653098464</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.0004500329960137606</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.0004646839806810021</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.007623023353517056</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.002360275713726878</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>7.006205851212144e-05</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>6.935921555850655e-05</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.0002031512995017692</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.001299104769714177</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.0001147912116721272</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.006107689812779427</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.0007646649610251188</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.002484212862327695</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.0005114799132570624</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0.0001600705145392567</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.002634393284097314</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.00155149563215673</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.00413855817168951</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.001100564026273787</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.001755411853082478</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.0003611503343563527</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.0002512158825993538</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.002588058123365045</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.0005307939718477428</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.0001240581768797711</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.0005562928272411227</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0.001259929267689586</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0.0008276699809357524</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.001120554748922586</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0.0004934861790388823</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0.005860590375959873</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0.0004573837504722178</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0.0008724581566639245</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0.0003041030722670257</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0.001048522302880883</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.001150148920714855</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.001071807346306741</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.0005514932563528419</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>6.601752829737961e-05</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.003086522687226534</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.002475551562383771</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.001532219350337982</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.0004681935533881187</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.001143314177170396</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0.0009660481009632349</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0.001770742237567902</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0.003253849456086755</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>2.907542511820793e-05</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.007084652781486511</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.00108628929592669</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0.004105788189917803</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0.002245956566184759</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0.001277740579098463</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0.00130665791220963</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0.0009940131567418575</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0.0006831081118434668</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0.0003154909354634583</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.003096276661381125</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.001724056201055646</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.001319956965744495</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0.000509822100866586</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0.0007075025350786746</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0.0007329521467909217</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0.001310821156948805</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>0.0004872124409303069</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0.001800043624825776</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0.002524408744648099</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.002827155403792858</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0.003003978403285146</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0.001634877407923341</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0.004418471828103065</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0.0006403762963600457</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.0001676390238571912</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>3.902279422618449e-05</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0.001579779200255871</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0.000420688244048506</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0.0002485996519681066</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.0008559813722968102</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0.0002220720052719116</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0.0004172367043793201</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0.002280912827700377</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0.0003686766431201249</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>0.0002046103472821414</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0.002077268902212381</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0.000597921316511929</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>0.00161919672973454</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0.000781803741119802</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0.0004434531438164413</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0.002384355291724205</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0.004377745091915131</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0.002357562305405736</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>0.0004445154336281121</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0.0002300165069755167</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0.002989474218338728</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>2.165979822166264e-06</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0.002061518374830484</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0.0007053990848362446</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0.0008128627669066191</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0.0004970524460077286</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>1.695571700111032e-05</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>0.001881683827377856</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0.000737865804694593</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0.002599112456664443</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0.00123006640933454</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0.001936716376803815</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0.0009430699283257127</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0.0007024399819783866</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0.0008824344840832055</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0.0009635252645239234</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>0.0003293846966698766</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>3.390584606677294e-05</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0.00392872141674161</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0.001955463085323572</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0.00120927719399333</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0.0002571793447714299</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0.0008087710593827069</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0.0006562296766787767</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0.0008483354467898607</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0.001000538701191545</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0.000135132810100913</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0.003184298519045115</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0.002211721614003181</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>5.080367554910481e-05</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0.0002507200697436929</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>1.263759986613877e-05</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0.0007384885102510452</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0.001169498427771032</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0.001745604909956455</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0.002381043042987585</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0.005965307354927063</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.001321720657870173</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0.002430688822641969</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0.001716079073958099</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0.001081929076462984</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0.003490752540528774</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0.0004967658314853907</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0.000320683466270566</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0.001038352027535439</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0.002583831548690796</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0.002270914381369948</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0.0009198586922138929</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0.0007328549399971962</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0.001538390526548028</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0.0005970312631689012</v>
       </c>
     </row>
   </sheetData>
